--- a/[Document]/소개운영자료/DIVE_개인정보_진로현황_수요조사.xlsx
+++ b/[Document]/소개운영자료/DIVE_개인정보_진로현황_수요조사.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="250">
   <si>
     <t>DIVE 2026년도 2분기 
 수요조사</t>
@@ -10317,11 +10317,11 @@
     <xf borderId="4" fillId="6" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="4" fillId="7" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="4" fillId="7" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="7" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="7" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10799,16 +10799,18 @@
       <c r="J5" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="K5" s="36"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
-      <c r="S5" s="36"/>
-      <c r="T5" s="36"/>
+      <c r="K5" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="37"/>
+      <c r="T5" s="37"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="32" t="s">
@@ -10841,22 +10843,22 @@
       <c r="J6" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="K6" s="36"/>
+      <c r="K6" s="37"/>
       <c r="L6" s="38"/>
       <c r="M6" s="39" t="s">
         <v>34</v>
       </c>
       <c r="N6" s="38"/>
       <c r="O6" s="38"/>
-      <c r="P6" s="37"/>
+      <c r="P6" s="36"/>
       <c r="Q6" s="40" t="s">
         <v>34</v>
       </c>
       <c r="R6" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="S6" s="36"/>
-      <c r="T6" s="36"/>
+      <c r="S6" s="37"/>
+      <c r="T6" s="37"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="32" t="s">
@@ -10890,15 +10892,17 @@
       <c r="K7" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="L7" s="38"/>
+      <c r="L7" s="39"/>
       <c r="M7" s="38"/>
       <c r="N7" s="38"/>
       <c r="O7" s="38"/>
       <c r="P7" s="38"/>
-      <c r="Q7" s="37"/>
-      <c r="R7" s="37"/>
-      <c r="S7" s="36"/>
-      <c r="T7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="S7" s="37"/>
+      <c r="T7" s="37"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="32" t="s">
@@ -10927,7 +10931,7 @@
         <v>67</v>
       </c>
       <c r="J8" s="26"/>
-      <c r="K8" s="36"/>
+      <c r="K8" s="37"/>
       <c r="L8" s="38"/>
       <c r="M8" s="38"/>
       <c r="N8" s="38"/>
@@ -10935,8 +10939,8 @@
       <c r="P8" s="38"/>
       <c r="Q8" s="38"/>
       <c r="R8" s="38"/>
-      <c r="S8" s="36"/>
-      <c r="T8" s="36"/>
+      <c r="S8" s="37"/>
+      <c r="T8" s="37"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="32" t="s">
@@ -10969,20 +10973,20 @@
       <c r="J9" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="K9" s="36"/>
+      <c r="K9" s="37"/>
       <c r="L9" s="38"/>
       <c r="M9" s="39" t="s">
         <v>34</v>
       </c>
       <c r="N9" s="38"/>
       <c r="O9" s="38"/>
-      <c r="P9" s="37"/>
+      <c r="P9" s="36"/>
       <c r="Q9" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="R9" s="37"/>
-      <c r="S9" s="36"/>
-      <c r="T9" s="36"/>
+      <c r="R9" s="36"/>
+      <c r="S9" s="37"/>
+      <c r="T9" s="37"/>
     </row>
     <row r="10" ht="14.25" hidden="1" customHeight="1">
       <c r="A10" s="32" t="s">
@@ -11067,8 +11071,8 @@
         <v>34</v>
       </c>
       <c r="R11" s="38"/>
-      <c r="S11" s="36"/>
-      <c r="T11" s="36"/>
+      <c r="S11" s="37"/>
+      <c r="T11" s="37"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="32" t="s">
@@ -11099,7 +11103,7 @@
         <v>95</v>
       </c>
       <c r="J12" s="35"/>
-      <c r="K12" s="36"/>
+      <c r="K12" s="37"/>
       <c r="L12" s="38"/>
       <c r="M12" s="38"/>
       <c r="N12" s="38"/>
@@ -11143,7 +11147,7 @@
         <v>102</v>
       </c>
       <c r="J13" s="35"/>
-      <c r="K13" s="36"/>
+      <c r="K13" s="37"/>
       <c r="L13" s="30" t="s">
         <v>34</v>
       </c>
@@ -11155,8 +11159,8 @@
       <c r="R13" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="S13" s="36"/>
-      <c r="T13" s="36"/>
+      <c r="S13" s="37"/>
+      <c r="T13" s="37"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="32" t="s">
@@ -11185,22 +11189,22 @@
         <v>108</v>
       </c>
       <c r="J14" s="35"/>
-      <c r="K14" s="36"/>
+      <c r="K14" s="37"/>
       <c r="L14" s="38"/>
       <c r="M14" s="40" t="s">
         <v>34</v>
       </c>
       <c r="N14" s="38"/>
       <c r="O14" s="38"/>
-      <c r="P14" s="37"/>
+      <c r="P14" s="36"/>
       <c r="Q14" s="40" t="s">
         <v>34</v>
       </c>
       <c r="R14" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="S14" s="36"/>
-      <c r="T14" s="36"/>
+      <c r="S14" s="37"/>
+      <c r="T14" s="37"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="32" t="s">
@@ -11229,14 +11233,18 @@
         <v>114</v>
       </c>
       <c r="J15" s="35"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="37"/>
-      <c r="M15" s="37"/>
-      <c r="N15" s="37"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="36"/>
+      <c r="M15" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="N15" s="36"/>
       <c r="O15" s="38"/>
       <c r="P15" s="38"/>
-      <c r="Q15" s="37"/>
-      <c r="R15" s="37"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="40" t="s">
+        <v>34</v>
+      </c>
       <c r="S15" s="30"/>
       <c r="T15" s="30"/>
     </row>
@@ -11267,7 +11275,7 @@
         <v>102</v>
       </c>
       <c r="J16" s="35"/>
-      <c r="K16" s="36"/>
+      <c r="K16" s="37"/>
       <c r="L16" s="38"/>
       <c r="M16" s="38"/>
       <c r="N16" s="38"/>
@@ -11275,8 +11283,8 @@
       <c r="P16" s="38"/>
       <c r="Q16" s="38"/>
       <c r="R16" s="38"/>
-      <c r="S16" s="36"/>
-      <c r="T16" s="36"/>
+      <c r="S16" s="37"/>
+      <c r="T16" s="37"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="32" t="s">
@@ -11307,7 +11315,7 @@
         <v>124</v>
       </c>
       <c r="J17" s="35"/>
-      <c r="K17" s="36"/>
+      <c r="K17" s="37"/>
       <c r="L17" s="38"/>
       <c r="M17" s="40" t="s">
         <v>34</v>
@@ -11323,8 +11331,8 @@
       <c r="R17" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="S17" s="36"/>
-      <c r="T17" s="36"/>
+      <c r="S17" s="37"/>
+      <c r="T17" s="37"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="32" t="s">
@@ -11353,7 +11361,7 @@
         <v>130</v>
       </c>
       <c r="J18" s="35"/>
-      <c r="K18" s="36"/>
+      <c r="K18" s="37"/>
       <c r="L18" s="38"/>
       <c r="M18" s="39" t="s">
         <v>34</v>
@@ -11363,8 +11371,8 @@
       <c r="P18" s="38"/>
       <c r="Q18" s="38"/>
       <c r="R18" s="38"/>
-      <c r="S18" s="36"/>
-      <c r="T18" s="36"/>
+      <c r="S18" s="37"/>
+      <c r="T18" s="37"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="E19" s="47"/>
@@ -14074,7 +14082,7 @@
       <c r="R6" s="38"/>
       <c r="S6" s="38"/>
       <c r="T6" s="38"/>
-      <c r="U6" s="36"/>
+      <c r="U6" s="37"/>
       <c r="V6" s="54" t="s">
         <v>34</v>
       </c>
@@ -14206,7 +14214,7 @@
       </c>
       <c r="S9" s="38"/>
       <c r="T9" s="38"/>
-      <c r="U9" s="36"/>
+      <c r="U9" s="37"/>
       <c r="V9" s="54" t="s">
         <v>34</v>
       </c>
@@ -14242,24 +14250,24 @@
       <c r="J10" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="K10" s="37"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
+      <c r="K10" s="36"/>
+      <c r="L10" s="36"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
       <c r="O10" s="56"/>
       <c r="P10" s="56"/>
       <c r="Q10" s="56"/>
-      <c r="R10" s="37" t="s">
+      <c r="R10" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="37" t="s">
+      <c r="S10" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="T10" s="37"/>
-      <c r="U10" s="36" t="s">
+      <c r="T10" s="36"/>
+      <c r="U10" s="37" t="s">
         <v>201</v>
       </c>
-      <c r="V10" s="36" t="s">
+      <c r="V10" s="37" t="s">
         <v>34</v>
       </c>
     </row>
@@ -14301,19 +14309,19 @@
       <c r="O11" s="53"/>
       <c r="P11" s="53"/>
       <c r="Q11" s="53"/>
-      <c r="R11" s="37" t="s">
+      <c r="R11" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="S11" s="37" t="s">
+      <c r="S11" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="T11" s="37" t="s">
+      <c r="T11" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="U11" s="36" t="s">
+      <c r="U11" s="37" t="s">
         <v>207</v>
       </c>
-      <c r="V11" s="36" t="s">
+      <c r="V11" s="37" t="s">
         <v>208</v>
       </c>
     </row>
@@ -14354,14 +14362,14 @@
       <c r="P12" s="53"/>
       <c r="Q12" s="53"/>
       <c r="R12" s="38"/>
-      <c r="S12" s="37" t="s">
+      <c r="S12" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="T12" s="37" t="s">
+      <c r="T12" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="U12" s="36"/>
-      <c r="V12" s="36" t="s">
+      <c r="U12" s="37"/>
+      <c r="V12" s="37" t="s">
         <v>213</v>
       </c>
     </row>
@@ -14402,8 +14410,8 @@
       <c r="R13" s="38"/>
       <c r="S13" s="38"/>
       <c r="T13" s="38"/>
-      <c r="U13" s="36"/>
-      <c r="V13" s="36" t="s">
+      <c r="U13" s="37"/>
+      <c r="V13" s="37" t="s">
         <v>218</v>
       </c>
     </row>
@@ -14445,15 +14453,15 @@
       <c r="O14" s="53"/>
       <c r="P14" s="53"/>
       <c r="Q14" s="53"/>
-      <c r="R14" s="37"/>
-      <c r="S14" s="37" t="s">
+      <c r="R14" s="36"/>
+      <c r="S14" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="T14" s="37" t="s">
+      <c r="T14" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="U14" s="36"/>
-      <c r="V14" s="36" t="s">
+      <c r="U14" s="37"/>
+      <c r="V14" s="37" t="s">
         <v>224</v>
       </c>
     </row>
@@ -14542,10 +14550,10 @@
         <v>34</v>
       </c>
       <c r="T16" s="38"/>
-      <c r="U16" s="36" t="s">
+      <c r="U16" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="V16" s="36" t="s">
+      <c r="V16" s="37" t="s">
         <v>233</v>
       </c>
     </row>
@@ -14595,7 +14603,7 @@
       <c r="S17" s="38"/>
       <c r="T17" s="38"/>
       <c r="U17" s="38"/>
-      <c r="V17" s="36" t="s">
+      <c r="V17" s="37" t="s">
         <v>237</v>
       </c>
     </row>
@@ -14637,11 +14645,11 @@
       <c r="Q18" s="53"/>
       <c r="R18" s="38"/>
       <c r="S18" s="38"/>
-      <c r="T18" s="37" t="s">
+      <c r="T18" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="U18" s="36"/>
-      <c r="V18" s="36"/>
+      <c r="U18" s="37"/>
+      <c r="V18" s="37"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="32" t="s">
@@ -14677,17 +14685,17 @@
       <c r="O19" s="53"/>
       <c r="P19" s="53"/>
       <c r="Q19" s="53"/>
-      <c r="R19" s="37" t="s">
+      <c r="R19" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="S19" s="37" t="s">
+      <c r="S19" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="T19" s="37" t="s">
+      <c r="T19" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="U19" s="36"/>
-      <c r="V19" s="36" t="s">
+      <c r="U19" s="37"/>
+      <c r="V19" s="37" t="s">
         <v>240</v>
       </c>
     </row>
@@ -14718,22 +14726,22 @@
         <v>114</v>
       </c>
       <c r="J20" s="55"/>
-      <c r="K20" s="37"/>
-      <c r="L20" s="37"/>
-      <c r="M20" s="37"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="36"/>
+      <c r="M20" s="36"/>
       <c r="N20" s="38"/>
       <c r="O20" s="53"/>
       <c r="P20" s="56"/>
       <c r="Q20" s="53"/>
       <c r="R20" s="38"/>
-      <c r="S20" s="37" t="s">
+      <c r="S20" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="T20" s="37" t="s">
+      <c r="T20" s="36" t="s">
         <v>34</v>
       </c>
       <c r="U20" s="30"/>
-      <c r="V20" s="36" t="s">
+      <c r="V20" s="37" t="s">
         <v>242</v>
       </c>
     </row>
@@ -14774,8 +14782,8 @@
       <c r="R21" s="38"/>
       <c r="S21" s="38"/>
       <c r="T21" s="38"/>
-      <c r="U21" s="36"/>
-      <c r="V21" s="36" t="s">
+      <c r="U21" s="37"/>
+      <c r="V21" s="37" t="s">
         <v>244</v>
       </c>
     </row>
@@ -14815,19 +14823,19 @@
       <c r="O22" s="50"/>
       <c r="P22" s="50"/>
       <c r="Q22" s="53"/>
-      <c r="R22" s="37" t="s">
+      <c r="R22" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="S22" s="37" t="s">
+      <c r="S22" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="T22" s="37" t="s">
+      <c r="T22" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="U22" s="36" t="s">
+      <c r="U22" s="37" t="s">
         <v>246</v>
       </c>
-      <c r="V22" s="36" t="s">
+      <c r="V22" s="37" t="s">
         <v>247</v>
       </c>
     </row>
@@ -14868,8 +14876,8 @@
       <c r="R23" s="38"/>
       <c r="S23" s="38"/>
       <c r="T23" s="38"/>
-      <c r="U23" s="36"/>
-      <c r="V23" s="36" t="s">
+      <c r="U23" s="37"/>
+      <c r="V23" s="37" t="s">
         <v>249</v>
       </c>
     </row>

--- a/[Document]/소개운영자료/DIVE_개인정보_진로현황_수요조사.xlsx
+++ b/[Document]/소개운영자료/DIVE_개인정보_진로현황_수요조사.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="252">
   <si>
     <t>DIVE 2026년도 2분기 
 수요조사</t>
@@ -35,10 +35,10 @@
     <t>필요시</t>
   </si>
   <si>
-    <t>Study Diving</t>
-  </si>
-  <si>
-    <t>Brand Diving</t>
+    <t>Study Diving (목요일 6시~)</t>
+  </si>
+  <si>
+    <t>Brand Diving (목요일 오전~)</t>
   </si>
   <si>
     <r>
@@ -3731,7 +3731,13 @@
 수요조사</t>
   </si>
   <si>
+    <t>Study Diving</t>
+  </si>
+  <si>
     <t>Project Diving</t>
+  </si>
+  <si>
+    <t>Brand Diving</t>
   </si>
   <si>
     <r>
@@ -10010,7 +10016,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -10069,6 +10075,12 @@
       <sz val="11.0"/>
       <color theme="0"/>
       <name val="Malgun Gothic"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -10214,7 +10226,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -10249,63 +10261,60 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="4" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="2" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="6" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="6" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="7" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="7" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="7" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="5" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="5" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -10317,7 +10326,10 @@
     <xf borderId="4" fillId="6" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="7" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="7" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="7" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="7" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -10329,10 +10341,10 @@
     <xf borderId="4" fillId="7" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="7" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="7" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="6" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="7" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -10344,43 +10356,46 @@
     <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="6" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="6" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="8" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="8" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="8" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="8" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="8" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="8" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="7" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="7" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="8" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="8" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="8" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="8" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10748,9 +10763,15 @@
       <c r="K4" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="30"/>
-      <c r="M4" s="31"/>
-      <c r="N4" s="30"/>
+      <c r="L4" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="29" t="s">
+        <v>34</v>
+      </c>
       <c r="O4" s="29" t="s">
         <v>35</v>
       </c>
@@ -10769,28 +10790,28 @@
       <c r="T4" s="29"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="31" t="s">
         <v>37</v>
       </c>
       <c r="B5" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="32">
         <v>2.02200803E8</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E5" s="33" t="s">
         <v>40</v>
       </c>
       <c r="F5" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="34" t="s">
+      <c r="G5" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="35" t="s">
+      <c r="H5" s="34" t="s">
         <v>43</v>
       </c>
       <c r="I5" s="26" t="s">
@@ -10799,7 +10820,7 @@
       <c r="J5" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="K5" s="31" t="s">
+      <c r="K5" s="35" t="s">
         <v>34</v>
       </c>
       <c r="L5" s="36"/>
@@ -10813,28 +10834,28 @@
       <c r="T5" s="37"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="31" t="s">
         <v>46</v>
       </c>
       <c r="B6" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="32">
         <v>2.02201788E8</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="E6" s="33" t="s">
         <v>48</v>
       </c>
       <c r="F6" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="35" t="s">
+      <c r="H6" s="34" t="s">
         <v>51</v>
       </c>
       <c r="I6" s="26" t="s">
@@ -10861,28 +10882,28 @@
       <c r="T6" s="37"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="31" t="s">
         <v>54</v>
       </c>
       <c r="B7" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="32">
         <v>2.02300502E8</v>
       </c>
-      <c r="E7" s="34" t="s">
+      <c r="E7" s="33" t="s">
         <v>57</v>
       </c>
       <c r="F7" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="G7" s="34" t="s">
+      <c r="G7" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="H7" s="35" t="s">
+      <c r="H7" s="34" t="s">
         <v>60</v>
       </c>
       <c r="I7" s="26" t="s">
@@ -10905,26 +10926,26 @@
       <c r="T7" s="37"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="31" t="s">
         <v>62</v>
       </c>
       <c r="B8" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="32">
         <v>2.02300733E8</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="E8" s="33" t="s">
         <v>64</v>
       </c>
       <c r="F8" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="G8" s="34"/>
-      <c r="H8" s="35" t="s">
+      <c r="G8" s="33"/>
+      <c r="H8" s="34" t="s">
         <v>66</v>
       </c>
       <c r="I8" s="26" t="s">
@@ -10943,16 +10964,16 @@
       <c r="T8" s="37"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="31" t="s">
         <v>68</v>
       </c>
       <c r="B9" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="32">
         <v>2.02300811E8</v>
       </c>
       <c r="E9" s="43" t="s">
@@ -10961,10 +10982,10 @@
       <c r="F9" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="G9" s="34" t="s">
+      <c r="G9" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="H9" s="35" t="s">
+      <c r="H9" s="34" t="s">
         <v>73</v>
       </c>
       <c r="I9" s="26" t="s">
@@ -10989,16 +11010,16 @@
       <c r="T9" s="37"/>
     </row>
     <row r="10" ht="14.25" hidden="1" customHeight="1">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="31" t="s">
         <v>76</v>
       </c>
       <c r="B10" s="21">
         <v>2025.0</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="32">
         <v>2.01901374E8</v>
       </c>
       <c r="E10" s="43" t="s">
@@ -11007,8 +11028,8 @@
       <c r="F10" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="G10" s="34"/>
-      <c r="H10" s="35" t="s">
+      <c r="G10" s="33"/>
+      <c r="H10" s="34" t="s">
         <v>80</v>
       </c>
       <c r="I10" s="26" t="s">
@@ -11017,7 +11038,7 @@
       <c r="J10" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="K10" s="34"/>
+      <c r="K10" s="33"/>
       <c r="L10" s="44"/>
       <c r="M10" s="44"/>
       <c r="N10" s="44"/>
@@ -11025,20 +11046,20 @@
       <c r="P10" s="44"/>
       <c r="Q10" s="44"/>
       <c r="R10" s="44"/>
-      <c r="S10" s="34"/>
-      <c r="T10" s="34"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="33"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="31" t="s">
         <v>83</v>
       </c>
       <c r="B11" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="32">
         <v>2.02202884E8</v>
       </c>
       <c r="E11" s="43" t="s">
@@ -11047,8 +11068,8 @@
       <c r="F11" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="G11" s="34"/>
-      <c r="H11" s="35" t="s">
+      <c r="G11" s="33"/>
+      <c r="H11" s="34" t="s">
         <v>80</v>
       </c>
       <c r="I11" s="26" t="s">
@@ -11064,10 +11085,10 @@
       <c r="M11" s="38"/>
       <c r="N11" s="38"/>
       <c r="O11" s="38"/>
-      <c r="P11" s="31" t="s">
+      <c r="P11" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="Q11" s="31" t="s">
+      <c r="Q11" s="35" t="s">
         <v>34</v>
       </c>
       <c r="R11" s="38"/>
@@ -11075,34 +11096,34 @@
       <c r="T11" s="37"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="31" t="s">
         <v>89</v>
       </c>
       <c r="B12" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="32">
         <v>2.02100256E8</v>
       </c>
-      <c r="E12" s="34" t="s">
+      <c r="E12" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="F12" s="34" t="s">
+      <c r="F12" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="34" t="s">
+      <c r="G12" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="H12" s="35" t="s">
+      <c r="H12" s="34" t="s">
         <v>94</v>
       </c>
       <c r="I12" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="J12" s="35"/>
+      <c r="J12" s="34"/>
       <c r="K12" s="37"/>
       <c r="L12" s="38"/>
       <c r="M12" s="38"/>
@@ -11119,34 +11140,34 @@
       <c r="T12" s="38"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="31" t="s">
         <v>96</v>
       </c>
       <c r="B13" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="32">
         <v>2.02100743E8</v>
       </c>
-      <c r="E13" s="34" t="s">
+      <c r="E13" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="F13" s="34" t="s">
+      <c r="F13" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="G13" s="34" t="s">
+      <c r="G13" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="H13" s="35" t="s">
+      <c r="H13" s="34" t="s">
         <v>101</v>
       </c>
       <c r="I13" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="J13" s="35"/>
+      <c r="J13" s="34"/>
       <c r="K13" s="37"/>
       <c r="L13" s="30" t="s">
         <v>34</v>
@@ -11163,32 +11184,32 @@
       <c r="T13" s="37"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="31" t="s">
         <v>103</v>
       </c>
       <c r="B14" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="32">
         <v>2.02200776E8</v>
       </c>
-      <c r="E14" s="34" t="s">
+      <c r="E14" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="F14" s="34" t="s">
+      <c r="F14" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="G14" s="34"/>
-      <c r="H14" s="35" t="s">
+      <c r="G14" s="33"/>
+      <c r="H14" s="34" t="s">
         <v>107</v>
       </c>
       <c r="I14" s="46" t="s">
         <v>108</v>
       </c>
-      <c r="J14" s="35"/>
+      <c r="J14" s="34"/>
       <c r="K14" s="37"/>
       <c r="L14" s="38"/>
       <c r="M14" s="40" t="s">
@@ -11207,32 +11228,32 @@
       <c r="T14" s="37"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="31" t="s">
         <v>109</v>
       </c>
       <c r="B15" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="32">
         <v>2.02201705E8</v>
       </c>
-      <c r="E15" s="34" t="s">
+      <c r="E15" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="F15" s="34" t="s">
+      <c r="F15" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="G15" s="34"/>
-      <c r="H15" s="35" t="s">
+      <c r="G15" s="33"/>
+      <c r="H15" s="34" t="s">
         <v>113</v>
       </c>
       <c r="I15" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="J15" s="35"/>
+      <c r="J15" s="34"/>
       <c r="K15" s="37"/>
       <c r="L15" s="36"/>
       <c r="M15" s="40" t="s">
@@ -11249,32 +11270,32 @@
       <c r="T15" s="30"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="31" t="s">
         <v>115</v>
       </c>
       <c r="B16" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="32">
         <v>2.02300822E8</v>
       </c>
-      <c r="E16" s="34" t="s">
+      <c r="E16" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="F16" s="34" t="s">
+      <c r="F16" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="G16" s="34"/>
-      <c r="H16" s="35" t="s">
+      <c r="G16" s="33"/>
+      <c r="H16" s="34" t="s">
         <v>101</v>
       </c>
       <c r="I16" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="J16" s="35"/>
+      <c r="J16" s="34"/>
       <c r="K16" s="37"/>
       <c r="L16" s="38"/>
       <c r="M16" s="38"/>
@@ -11287,34 +11308,34 @@
       <c r="T16" s="37"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="31" t="s">
         <v>119</v>
       </c>
       <c r="B17" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="32">
         <v>2.02301275E8</v>
       </c>
-      <c r="E17" s="34" t="s">
+      <c r="E17" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="F17" s="34" t="s">
+      <c r="F17" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="G17" s="34" t="s">
+      <c r="G17" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="H17" s="35" t="s">
+      <c r="H17" s="34" t="s">
         <v>80</v>
       </c>
       <c r="I17" s="46" t="s">
         <v>124</v>
       </c>
-      <c r="J17" s="35"/>
+      <c r="J17" s="34"/>
       <c r="K17" s="37"/>
       <c r="L17" s="38"/>
       <c r="M17" s="40" t="s">
@@ -11335,32 +11356,32 @@
       <c r="T17" s="37"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="31" t="s">
         <v>125</v>
       </c>
       <c r="B18" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="32">
         <v>2.02401802E8</v>
       </c>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="F18" s="34" t="s">
+      <c r="F18" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="G18" s="34"/>
-      <c r="H18" s="35" t="s">
+      <c r="G18" s="33"/>
+      <c r="H18" s="34" t="s">
         <v>129</v>
       </c>
       <c r="I18" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="J18" s="35"/>
+      <c r="J18" s="34"/>
       <c r="K18" s="37"/>
       <c r="L18" s="38"/>
       <c r="M18" s="39" t="s">
@@ -13842,87 +13863,87 @@
       </c>
       <c r="I2" s="10"/>
       <c r="J2" s="11"/>
-      <c r="K2" s="13" t="s">
-        <v>4</v>
+      <c r="K2" s="48" t="s">
+        <v>132</v>
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="3"/>
-      <c r="O2" s="13" t="s">
-        <v>132</v>
+      <c r="O2" s="48" t="s">
+        <v>133</v>
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="3"/>
-      <c r="R2" s="13" t="s">
-        <v>5</v>
+      <c r="R2" s="48" t="s">
+        <v>134</v>
       </c>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="3"/>
       <c r="V2" s="18" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G3" s="16" t="s">
         <v>12</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L3" s="18" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N3" s="18" t="s">
         <v>20</v>
       </c>
       <c r="O3" s="18" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P3" s="18" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q3" s="18" t="s">
         <v>20</v>
       </c>
       <c r="R3" s="18" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="S3" s="18" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="T3" s="18" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="U3" s="18" t="s">
         <v>24</v>
@@ -13953,35 +13974,35 @@
       <c r="G4" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="48" t="s">
-        <v>151</v>
-      </c>
-      <c r="I4" s="48" t="s">
-        <v>152</v>
-      </c>
-      <c r="J4" s="49" t="s">
+      <c r="H4" s="49" t="s">
         <v>153</v>
       </c>
+      <c r="I4" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="J4" s="50" t="s">
+        <v>155</v>
+      </c>
       <c r="K4" s="30" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L4" s="30" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M4" s="30" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N4" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="O4" s="50" t="s">
+      <c r="O4" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P4" s="50" t="s">
+      <c r="P4" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="Q4" s="51" t="s">
-        <v>157</v>
+      <c r="Q4" s="52" t="s">
+        <v>159</v>
       </c>
       <c r="R4" s="30" t="s">
         <v>34</v>
@@ -14000,34 +14021,34 @@
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="32" t="s">
-        <v>158</v>
+      <c r="A5" s="31" t="s">
+        <v>160</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>160</v>
+        <v>161</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>162</v>
       </c>
       <c r="D5" s="23">
         <v>2.01800875E8</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="H5" s="48" t="s">
-        <v>164</v>
-      </c>
-      <c r="I5" s="48" t="s">
         <v>165</v>
       </c>
-      <c r="J5" s="48"/>
+      <c r="H5" s="49" t="s">
+        <v>166</v>
+      </c>
+      <c r="I5" s="49" t="s">
+        <v>167</v>
+      </c>
+      <c r="J5" s="49"/>
       <c r="K5" s="44"/>
       <c r="L5" s="44"/>
       <c r="M5" s="44"/>
@@ -14038,82 +14059,82 @@
       <c r="R5" s="44"/>
       <c r="S5" s="44"/>
       <c r="T5" s="44"/>
-      <c r="U5" s="34"/>
-      <c r="V5" s="34"/>
+      <c r="U5" s="33"/>
+      <c r="V5" s="33"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="32" t="s">
-        <v>166</v>
+      <c r="A6" s="31" t="s">
+        <v>168</v>
       </c>
       <c r="B6" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="33" t="s">
-        <v>167</v>
+      <c r="C6" s="32" t="s">
+        <v>169</v>
       </c>
       <c r="D6" s="23">
         <v>2.0210079E8</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="F6" s="52" t="s">
-        <v>169</v>
+        <v>170</v>
+      </c>
+      <c r="F6" s="53" t="s">
+        <v>171</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="H6" s="48" t="s">
-        <v>171</v>
-      </c>
-      <c r="I6" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="J6" s="48" t="s">
+      <c r="H6" s="49" t="s">
         <v>173</v>
+      </c>
+      <c r="I6" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="J6" s="49" t="s">
+        <v>175</v>
       </c>
       <c r="K6" s="38"/>
       <c r="L6" s="38"/>
       <c r="M6" s="38"/>
       <c r="N6" s="38"/>
-      <c r="O6" s="53"/>
-      <c r="P6" s="53"/>
-      <c r="Q6" s="53"/>
+      <c r="O6" s="54"/>
+      <c r="P6" s="54"/>
+      <c r="Q6" s="54"/>
       <c r="R6" s="38"/>
       <c r="S6" s="38"/>
       <c r="T6" s="38"/>
       <c r="U6" s="37"/>
-      <c r="V6" s="54" t="s">
+      <c r="V6" s="55" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="32" t="s">
-        <v>174</v>
+      <c r="A7" s="31" t="s">
+        <v>176</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>176</v>
+        <v>177</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>178</v>
       </c>
       <c r="D7" s="23">
         <v>2.02100794E8</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G7" s="24"/>
-      <c r="H7" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="I7" s="48" t="s">
-        <v>180</v>
-      </c>
-      <c r="J7" s="48"/>
+      <c r="H7" s="49" t="s">
+        <v>181</v>
+      </c>
+      <c r="I7" s="49" t="s">
+        <v>182</v>
+      </c>
+      <c r="J7" s="49"/>
       <c r="K7" s="44"/>
       <c r="L7" s="44"/>
       <c r="M7" s="44"/>
@@ -14124,39 +14145,39 @@
       <c r="R7" s="44"/>
       <c r="S7" s="44"/>
       <c r="T7" s="44"/>
-      <c r="U7" s="34"/>
-      <c r="V7" s="34"/>
+      <c r="U7" s="33"/>
+      <c r="V7" s="33"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="32" t="s">
-        <v>181</v>
+      <c r="A8" s="31" t="s">
+        <v>183</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>182</v>
-      </c>
-      <c r="D8" s="33">
+        <v>177</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="32">
         <v>2.01900884E8</v>
       </c>
-      <c r="E8" s="34" t="s">
-        <v>183</v>
+      <c r="E8" s="33" t="s">
+        <v>185</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="G8" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="H8" s="48" t="s">
-        <v>185</v>
-      </c>
-      <c r="I8" s="48" t="s">
         <v>186</v>
       </c>
-      <c r="J8" s="48" t="s">
+      <c r="G8" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="H8" s="49" t="s">
         <v>187</v>
+      </c>
+      <c r="I8" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="J8" s="49" t="s">
+        <v>189</v>
       </c>
       <c r="K8" s="44"/>
       <c r="L8" s="44"/>
@@ -14168,95 +14189,95 @@
       <c r="R8" s="44"/>
       <c r="S8" s="44"/>
       <c r="T8" s="44"/>
-      <c r="U8" s="34"/>
-      <c r="V8" s="34"/>
+      <c r="U8" s="33"/>
+      <c r="V8" s="33"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="32" t="s">
-        <v>188</v>
+      <c r="A9" s="31" t="s">
+        <v>190</v>
       </c>
       <c r="B9" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="D9" s="33">
+      <c r="C9" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="D9" s="32">
         <v>2.01900833E8</v>
       </c>
       <c r="E9" s="43" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>191</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>192</v>
-      </c>
-      <c r="H9" s="55" t="s">
         <v>193</v>
       </c>
-      <c r="I9" s="48" t="s">
+      <c r="G9" s="33" t="s">
         <v>194</v>
       </c>
-      <c r="J9" s="48" t="s">
+      <c r="H9" s="56" t="s">
         <v>195</v>
+      </c>
+      <c r="I9" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="J9" s="49" t="s">
+        <v>197</v>
       </c>
       <c r="K9" s="38"/>
       <c r="L9" s="38"/>
       <c r="M9" s="38"/>
       <c r="N9" s="38"/>
-      <c r="O9" s="53"/>
-      <c r="P9" s="53"/>
-      <c r="Q9" s="53"/>
+      <c r="O9" s="54"/>
+      <c r="P9" s="54"/>
+      <c r="Q9" s="54"/>
       <c r="R9" s="30" t="s">
         <v>34</v>
       </c>
       <c r="S9" s="38"/>
       <c r="T9" s="38"/>
       <c r="U9" s="37"/>
-      <c r="V9" s="54" t="s">
+      <c r="V9" s="55" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="32" t="s">
-        <v>196</v>
+      <c r="A10" s="31" t="s">
+        <v>198</v>
       </c>
       <c r="B10" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="D10" s="33">
+      <c r="C10" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="D10" s="32">
         <v>2.02200803E8</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="E10" s="33" t="s">
         <v>40</v>
       </c>
       <c r="F10" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="34" t="s">
+      <c r="G10" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="H10" s="55" t="s">
-        <v>198</v>
-      </c>
-      <c r="I10" s="48" t="s">
-        <v>199</v>
-      </c>
-      <c r="J10" s="48" t="s">
+      <c r="H10" s="56" t="s">
         <v>200</v>
+      </c>
+      <c r="I10" s="49" t="s">
+        <v>201</v>
+      </c>
+      <c r="J10" s="49" t="s">
+        <v>202</v>
       </c>
       <c r="K10" s="36"/>
       <c r="L10" s="36"/>
       <c r="M10" s="36"/>
       <c r="N10" s="36"/>
-      <c r="O10" s="56"/>
-      <c r="P10" s="56"/>
-      <c r="Q10" s="56"/>
+      <c r="O10" s="57"/>
+      <c r="P10" s="57"/>
+      <c r="Q10" s="57"/>
       <c r="R10" s="36" t="s">
         <v>34</v>
       </c>
@@ -14265,50 +14286,50 @@
       </c>
       <c r="T10" s="36"/>
       <c r="U10" s="37" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="V10" s="37" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="32" t="s">
-        <v>202</v>
+      <c r="A11" s="31" t="s">
+        <v>204</v>
       </c>
       <c r="B11" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="D11" s="33">
+      <c r="C11" s="32" t="s">
+        <v>205</v>
+      </c>
+      <c r="D11" s="32">
         <v>2.02201788E8</v>
       </c>
-      <c r="E11" s="34" t="s">
+      <c r="E11" s="33" t="s">
         <v>48</v>
       </c>
       <c r="F11" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="G11" s="34" t="s">
+      <c r="G11" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="H11" s="55" t="s">
-        <v>204</v>
-      </c>
-      <c r="I11" s="48" t="s">
-        <v>205</v>
-      </c>
-      <c r="J11" s="48" t="s">
+      <c r="H11" s="56" t="s">
         <v>206</v>
+      </c>
+      <c r="I11" s="49" t="s">
+        <v>207</v>
+      </c>
+      <c r="J11" s="49" t="s">
+        <v>208</v>
       </c>
       <c r="K11" s="38"/>
       <c r="L11" s="38"/>
       <c r="M11" s="38"/>
       <c r="N11" s="38"/>
-      <c r="O11" s="53"/>
-      <c r="P11" s="53"/>
-      <c r="Q11" s="53"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="54"/>
+      <c r="Q11" s="54"/>
       <c r="R11" s="36" t="s">
         <v>34</v>
       </c>
@@ -14319,48 +14340,48 @@
         <v>34</v>
       </c>
       <c r="U11" s="37" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="V11" s="37" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="32" t="s">
-        <v>209</v>
+      <c r="A12" s="31" t="s">
+        <v>211</v>
       </c>
       <c r="B12" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="D12" s="33">
+      <c r="C12" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="D12" s="32">
         <v>2.02300502E8</v>
       </c>
-      <c r="E12" s="34" t="s">
+      <c r="E12" s="33" t="s">
         <v>57</v>
       </c>
       <c r="F12" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="34" t="s">
+      <c r="G12" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="55" t="s">
-        <v>211</v>
-      </c>
-      <c r="I12" s="48" t="s">
-        <v>212</v>
-      </c>
-      <c r="J12" s="49"/>
+      <c r="H12" s="56" t="s">
+        <v>213</v>
+      </c>
+      <c r="I12" s="49" t="s">
+        <v>214</v>
+      </c>
+      <c r="J12" s="50"/>
       <c r="K12" s="38"/>
       <c r="L12" s="38"/>
       <c r="M12" s="38"/>
       <c r="N12" s="38"/>
-      <c r="O12" s="53"/>
-      <c r="P12" s="53"/>
-      <c r="Q12" s="53"/>
+      <c r="O12" s="54"/>
+      <c r="P12" s="54"/>
+      <c r="Q12" s="54"/>
       <c r="R12" s="38"/>
       <c r="S12" s="36" t="s">
         <v>34</v>
@@ -14370,62 +14391,62 @@
       </c>
       <c r="U12" s="37"/>
       <c r="V12" s="37" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="32" t="s">
-        <v>214</v>
+      <c r="A13" s="31" t="s">
+        <v>216</v>
       </c>
       <c r="B13" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="33" t="s">
-        <v>215</v>
-      </c>
-      <c r="D13" s="33">
+      <c r="C13" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="D13" s="32">
         <v>2.02300733E8</v>
       </c>
-      <c r="E13" s="34" t="s">
+      <c r="E13" s="33" t="s">
         <v>64</v>
       </c>
       <c r="F13" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="G13" s="34"/>
-      <c r="H13" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="I13" s="48" t="s">
-        <v>217</v>
-      </c>
-      <c r="J13" s="48"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="56" t="s">
+        <v>218</v>
+      </c>
+      <c r="I13" s="49" t="s">
+        <v>219</v>
+      </c>
+      <c r="J13" s="49"/>
       <c r="K13" s="38"/>
       <c r="L13" s="38"/>
       <c r="M13" s="38"/>
       <c r="N13" s="38"/>
-      <c r="O13" s="53"/>
-      <c r="P13" s="53"/>
-      <c r="Q13" s="53"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
       <c r="R13" s="38"/>
       <c r="S13" s="38"/>
       <c r="T13" s="38"/>
       <c r="U13" s="37"/>
       <c r="V13" s="37" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="32" t="s">
-        <v>219</v>
+      <c r="A14" s="31" t="s">
+        <v>221</v>
       </c>
       <c r="B14" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="33" t="s">
-        <v>220</v>
-      </c>
-      <c r="D14" s="33">
+      <c r="C14" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="D14" s="32">
         <v>2.02300811E8</v>
       </c>
       <c r="E14" s="43" t="s">
@@ -14434,25 +14455,25 @@
       <c r="F14" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="G14" s="34" t="s">
+      <c r="G14" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="H14" s="55" t="s">
-        <v>221</v>
-      </c>
-      <c r="I14" s="48" t="s">
-        <v>222</v>
-      </c>
-      <c r="J14" s="48" t="s">
+      <c r="H14" s="56" t="s">
         <v>223</v>
+      </c>
+      <c r="I14" s="49" t="s">
+        <v>224</v>
+      </c>
+      <c r="J14" s="49" t="s">
+        <v>225</v>
       </c>
       <c r="K14" s="38"/>
       <c r="L14" s="38"/>
       <c r="M14" s="38"/>
       <c r="N14" s="38"/>
-      <c r="O14" s="53"/>
-      <c r="P14" s="53"/>
-      <c r="Q14" s="53"/>
+      <c r="O14" s="54"/>
+      <c r="P14" s="54"/>
+      <c r="Q14" s="54"/>
       <c r="R14" s="36"/>
       <c r="S14" s="36" t="s">
         <v>34</v>
@@ -14462,20 +14483,20 @@
       </c>
       <c r="U14" s="37"/>
       <c r="V14" s="37" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="32" t="s">
-        <v>225</v>
+      <c r="A15" s="31" t="s">
+        <v>227</v>
       </c>
       <c r="B15" s="21">
         <v>2025.0</v>
       </c>
-      <c r="C15" s="33" t="s">
-        <v>226</v>
-      </c>
-      <c r="D15" s="33">
+      <c r="C15" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="D15" s="32">
         <v>2.01901374E8</v>
       </c>
       <c r="E15" s="43" t="s">
@@ -14484,15 +14505,15 @@
       <c r="F15" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="34"/>
-      <c r="H15" s="55" t="s">
+      <c r="G15" s="33"/>
+      <c r="H15" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="I15" s="48" t="s">
-        <v>227</v>
-      </c>
-      <c r="J15" s="48" t="s">
-        <v>228</v>
+      <c r="I15" s="49" t="s">
+        <v>229</v>
+      </c>
+      <c r="J15" s="49" t="s">
+        <v>230</v>
       </c>
       <c r="K15" s="44"/>
       <c r="L15" s="44"/>
@@ -14504,20 +14525,20 @@
       <c r="R15" s="44"/>
       <c r="S15" s="44"/>
       <c r="T15" s="44"/>
-      <c r="U15" s="34"/>
-      <c r="V15" s="34"/>
+      <c r="U15" s="33"/>
+      <c r="V15" s="33"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="32" t="s">
-        <v>229</v>
+      <c r="A16" s="31" t="s">
+        <v>231</v>
       </c>
       <c r="B16" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="33" t="s">
-        <v>230</v>
-      </c>
-      <c r="D16" s="33">
+      <c r="C16" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="D16" s="32">
         <v>2.02202884E8</v>
       </c>
       <c r="E16" s="43" t="s">
@@ -14526,23 +14547,23 @@
       <c r="F16" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="G16" s="34"/>
-      <c r="H16" s="55" t="s">
+      <c r="G16" s="33"/>
+      <c r="H16" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="I16" s="48" t="s">
+      <c r="I16" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="J16" s="48" t="s">
-        <v>231</v>
+      <c r="J16" s="49" t="s">
+        <v>233</v>
       </c>
       <c r="K16" s="38"/>
       <c r="L16" s="38"/>
       <c r="M16" s="38"/>
       <c r="N16" s="38"/>
-      <c r="O16" s="53"/>
-      <c r="P16" s="53"/>
-      <c r="Q16" s="53"/>
+      <c r="O16" s="54"/>
+      <c r="P16" s="54"/>
+      <c r="Q16" s="54"/>
       <c r="R16" s="30" t="s">
         <v>34</v>
       </c>
@@ -14551,41 +14572,41 @@
       </c>
       <c r="T16" s="38"/>
       <c r="U16" s="37" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="V16" s="37" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="32" t="s">
-        <v>234</v>
+      <c r="A17" s="31" t="s">
+        <v>236</v>
       </c>
       <c r="B17" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="32">
         <v>2.02100256E8</v>
       </c>
-      <c r="E17" s="34" t="s">
+      <c r="E17" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="F17" s="34" t="s">
+      <c r="F17" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="G17" s="34" t="s">
+      <c r="G17" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="H17" s="55" t="s">
-        <v>235</v>
-      </c>
-      <c r="I17" s="57" t="s">
-        <v>236</v>
-      </c>
-      <c r="J17" s="55"/>
+      <c r="H17" s="56" t="s">
+        <v>237</v>
+      </c>
+      <c r="I17" s="58" t="s">
+        <v>238</v>
+      </c>
+      <c r="J17" s="56"/>
       <c r="K17" s="38" t="s">
         <v>34</v>
       </c>
@@ -14596,53 +14617,53 @@
         <v>34</v>
       </c>
       <c r="N17" s="38"/>
-      <c r="O17" s="53"/>
-      <c r="P17" s="53"/>
-      <c r="Q17" s="53"/>
+      <c r="O17" s="54"/>
+      <c r="P17" s="54"/>
+      <c r="Q17" s="54"/>
       <c r="R17" s="38"/>
       <c r="S17" s="38"/>
       <c r="T17" s="38"/>
       <c r="U17" s="38"/>
       <c r="V17" s="37" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="32" t="s">
-        <v>238</v>
+      <c r="A18" s="31" t="s">
+        <v>240</v>
       </c>
       <c r="B18" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="32">
         <v>2.02100743E8</v>
       </c>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="F18" s="34" t="s">
+      <c r="F18" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="G18" s="34" t="s">
+      <c r="G18" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="H18" s="55" t="s">
+      <c r="H18" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="I18" s="57" t="s">
+      <c r="I18" s="58" t="s">
         <v>102</v>
       </c>
-      <c r="J18" s="55"/>
+      <c r="J18" s="56"/>
       <c r="K18" s="38"/>
       <c r="L18" s="38"/>
       <c r="M18" s="38"/>
       <c r="N18" s="38"/>
-      <c r="O18" s="53"/>
-      <c r="P18" s="50"/>
-      <c r="Q18" s="53"/>
+      <c r="O18" s="54"/>
+      <c r="P18" s="51"/>
+      <c r="Q18" s="54"/>
       <c r="R18" s="38"/>
       <c r="S18" s="38"/>
       <c r="T18" s="36" t="s">
@@ -14652,39 +14673,39 @@
       <c r="V18" s="37"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="32" t="s">
-        <v>239</v>
+      <c r="A19" s="31" t="s">
+        <v>241</v>
       </c>
       <c r="B19" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="33">
+      <c r="D19" s="32">
         <v>2.02200776E8</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="E19" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="F19" s="34" t="s">
+      <c r="F19" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="G19" s="34"/>
-      <c r="H19" s="55" t="s">
+      <c r="G19" s="33"/>
+      <c r="H19" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="I19" s="57" t="s">
+      <c r="I19" s="58" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="55"/>
+      <c r="J19" s="56"/>
       <c r="K19" s="38"/>
       <c r="L19" s="38"/>
       <c r="M19" s="38"/>
       <c r="N19" s="38"/>
-      <c r="O19" s="53"/>
-      <c r="P19" s="53"/>
-      <c r="Q19" s="53"/>
+      <c r="O19" s="54"/>
+      <c r="P19" s="54"/>
+      <c r="Q19" s="54"/>
       <c r="R19" s="36" t="s">
         <v>34</v>
       </c>
@@ -14696,43 +14717,43 @@
       </c>
       <c r="U19" s="37"/>
       <c r="V19" s="37" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="32" t="s">
-        <v>241</v>
+      <c r="A20" s="31" t="s">
+        <v>243</v>
       </c>
       <c r="B20" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="33" t="s">
+      <c r="C20" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="32">
         <v>2.02201705E8</v>
       </c>
-      <c r="E20" s="34" t="s">
+      <c r="E20" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="F20" s="34" t="s">
+      <c r="F20" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="G20" s="34"/>
-      <c r="H20" s="55" t="s">
+      <c r="G20" s="33"/>
+      <c r="H20" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="I20" s="57" t="s">
+      <c r="I20" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="J20" s="55"/>
+      <c r="J20" s="56"/>
       <c r="K20" s="36"/>
       <c r="L20" s="36"/>
       <c r="M20" s="36"/>
       <c r="N20" s="38"/>
-      <c r="O20" s="53"/>
-      <c r="P20" s="56"/>
-      <c r="Q20" s="53"/>
+      <c r="O20" s="54"/>
+      <c r="P20" s="57"/>
+      <c r="Q20" s="54"/>
       <c r="R20" s="38"/>
       <c r="S20" s="36" t="s">
         <v>34</v>
@@ -14742,87 +14763,87 @@
       </c>
       <c r="U20" s="30"/>
       <c r="V20" s="37" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="32" t="s">
-        <v>243</v>
+      <c r="A21" s="31" t="s">
+        <v>245</v>
       </c>
       <c r="B21" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="32">
         <v>2.02300822E8</v>
       </c>
-      <c r="E21" s="34" t="s">
+      <c r="E21" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="F21" s="34" t="s">
+      <c r="F21" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="G21" s="34"/>
-      <c r="H21" s="55" t="s">
+      <c r="G21" s="33"/>
+      <c r="H21" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="I21" s="57" t="s">
+      <c r="I21" s="58" t="s">
         <v>102</v>
       </c>
-      <c r="J21" s="55"/>
+      <c r="J21" s="56"/>
       <c r="K21" s="38"/>
       <c r="L21" s="38"/>
       <c r="M21" s="38"/>
       <c r="N21" s="38"/>
-      <c r="O21" s="53"/>
-      <c r="P21" s="53"/>
-      <c r="Q21" s="53"/>
+      <c r="O21" s="54"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="54"/>
       <c r="R21" s="38"/>
       <c r="S21" s="38"/>
       <c r="T21" s="38"/>
       <c r="U21" s="37"/>
       <c r="V21" s="37" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="32" t="s">
-        <v>245</v>
+      <c r="A22" s="31" t="s">
+        <v>247</v>
       </c>
       <c r="B22" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="32">
         <v>2.02301275E8</v>
       </c>
-      <c r="E22" s="34" t="s">
+      <c r="E22" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="F22" s="34" t="s">
+      <c r="F22" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="G22" s="34" t="s">
+      <c r="G22" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="H22" s="55" t="s">
+      <c r="H22" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="I22" s="57" t="s">
+      <c r="I22" s="58" t="s">
         <v>124</v>
       </c>
-      <c r="J22" s="55"/>
+      <c r="J22" s="56"/>
       <c r="K22" s="38"/>
       <c r="L22" s="38"/>
       <c r="M22" s="38"/>
       <c r="N22" s="38"/>
-      <c r="O22" s="50"/>
-      <c r="P22" s="50"/>
-      <c r="Q22" s="53"/>
+      <c r="O22" s="51"/>
+      <c r="P22" s="51"/>
+      <c r="Q22" s="54"/>
       <c r="R22" s="36" t="s">
         <v>34</v>
       </c>
@@ -14833,52 +14854,52 @@
         <v>34</v>
       </c>
       <c r="U22" s="37" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="V22" s="37" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="32" t="s">
-        <v>248</v>
+      <c r="A23" s="31" t="s">
+        <v>250</v>
       </c>
       <c r="B23" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="D23" s="33">
+      <c r="D23" s="32">
         <v>2.02401802E8</v>
       </c>
-      <c r="E23" s="34" t="s">
+      <c r="E23" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="F23" s="34" t="s">
+      <c r="F23" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="G23" s="34"/>
-      <c r="H23" s="55" t="s">
+      <c r="G23" s="33"/>
+      <c r="H23" s="56" t="s">
         <v>129</v>
       </c>
-      <c r="I23" s="57" t="s">
+      <c r="I23" s="58" t="s">
         <v>130</v>
       </c>
-      <c r="J23" s="55"/>
+      <c r="J23" s="56"/>
       <c r="K23" s="38"/>
       <c r="L23" s="38"/>
       <c r="M23" s="38"/>
       <c r="N23" s="38"/>
-      <c r="O23" s="53"/>
-      <c r="P23" s="53"/>
-      <c r="Q23" s="53"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="54"/>
       <c r="R23" s="38"/>
       <c r="S23" s="38"/>
       <c r="T23" s="38"/>
       <c r="U23" s="37"/>
       <c r="V23" s="37" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">

--- a/[Document]/소개운영자료/DIVE_개인정보_진로현황_수요조사.xlsx
+++ b/[Document]/소개운영자료/DIVE_개인정보_진로현황_수요조사.xlsx
@@ -11169,10 +11169,10 @@
       </c>
       <c r="J13" s="34"/>
       <c r="K13" s="37"/>
-      <c r="L13" s="30" t="s">
+      <c r="L13" s="30"/>
+      <c r="M13" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="M13" s="38"/>
       <c r="N13" s="38"/>
       <c r="O13" s="38"/>
       <c r="P13" s="38"/>

--- a/[Document]/소개운영자료/DIVE_개인정보_진로현황_수요조사.xlsx
+++ b/[Document]/소개운영자료/DIVE_개인정보_진로현황_수요조사.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DataScience\[DIVE]\[Document]\소개운영자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91AB5FED-D50D-4386-BA13-0EF449F3E117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD199B00-DB8E-4E81-A54E-E5939B8D84EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31890" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10507,13 +10507,13 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>논문 1건</t>
+      <t>한국경영학회 논문 1건</t>
     </r>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">1. KCI </t>
+      <t xml:space="preserve">1. </t>
     </r>
     <r>
       <rPr>
@@ -10523,13 +10523,14 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>한국경영학회 논문 1건</t>
+      <t>공모전 수상 1건
+2. KCI 학회 논문 1건</t>
     </r>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">1. HCI </t>
+      <t xml:space="preserve">1. </t>
     </r>
     <r>
       <rPr>
@@ -10539,8 +10540,88 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>학술대회 발표 1건
-2. KCI</t>
+      <t>공모전 수상 1건</t>
+    </r>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공모전</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>건</t>
+    </r>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마케팅연구/한국경영과학회</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 발표 1건
+2. KCI HCI</t>
     </r>
     <r>
       <rPr>
@@ -10566,7 +10647,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">1. </t>
+      <t xml:space="preserve">1. KCI </t>
     </r>
     <r>
       <rPr>
@@ -10576,78 +10657,8 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>공모전 수상 1건
-2. KCI 학회 논문 1건</t>
-    </r>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>공모전 수상 1건</t>
-    </r>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>공모전</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>건</t>
+      <t>논문 1건
+- 데이터: https://drive.google.com/drive/folders/1cX1QUZgE5ZihPZmlJxIcao_KCacXF8vR</t>
     </r>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
@@ -10656,7 +10667,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10865,6 +10876,13 @@
       <name val="Calibri"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -11134,6 +11152,15 @@
     <xf numFmtId="0" fontId="16" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -11144,12 +11171,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -11164,10 +11185,7 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -11402,11 +11420,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="18">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="47"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="50"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -11421,34 +11439,34 @@
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
       <c r="I2" s="6"/>
       <c r="J2" s="7"/>
       <c r="K2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="54" t="s">
+      <c r="L2" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="50" t="s">
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="57"/>
+      <c r="Q2" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="R2" s="53"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
+      <c r="R2" s="54"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
     </row>
     <row r="3" spans="1:21" ht="84.4">
       <c r="A3" s="9" t="s">
@@ -11496,7 +11514,7 @@
       <c r="O3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="P3" s="57" t="s">
+      <c r="P3" s="46" t="s">
         <v>252</v>
       </c>
       <c r="Q3" s="12" t="s">
@@ -11511,7 +11529,7 @@
       <c r="T3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="U3" s="58" t="s">
+      <c r="U3" s="47" t="s">
         <v>252</v>
       </c>
     </row>
@@ -11668,8 +11686,8 @@
         <v>34</v>
       </c>
       <c r="T6" s="29"/>
-      <c r="U6" s="52" t="s">
-        <v>256</v>
+      <c r="U6" s="45" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="50.65">
@@ -11801,8 +11819,8 @@
       </c>
       <c r="S9" s="28"/>
       <c r="T9" s="29"/>
-      <c r="U9" s="52" t="s">
-        <v>255</v>
+      <c r="U9" s="45" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="28.5">
@@ -11891,8 +11909,8 @@
       </c>
       <c r="S11" s="30"/>
       <c r="T11" s="29"/>
-      <c r="U11" s="52" t="s">
-        <v>254</v>
+      <c r="U11" s="45" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="33.75">
@@ -11983,11 +12001,11 @@
         <v>34</v>
       </c>
       <c r="T13" s="29"/>
-      <c r="U13" s="52" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" ht="28.5">
+      <c r="U13" s="45" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="84.4">
       <c r="A14" s="24" t="s">
         <v>103</v>
       </c>
@@ -12030,8 +12048,8 @@
         <v>34</v>
       </c>
       <c r="T14" s="29"/>
-      <c r="U14" s="52" t="s">
-        <v>253</v>
+      <c r="U14" s="45" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="33.75">
@@ -12075,8 +12093,8 @@
         <v>34</v>
       </c>
       <c r="T15" s="23"/>
-      <c r="U15" s="52" t="s">
-        <v>257</v>
+      <c r="U15" s="45" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="28.5">
@@ -13871,11 +13889,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="14.25" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="47"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="50"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -13888,34 +13906,34 @@
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
       <c r="I2" s="6"/>
       <c r="J2" s="7"/>
-      <c r="K2" s="51" t="s">
+      <c r="K2" s="58" t="s">
         <v>132</v>
       </c>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="51" t="s">
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="58" t="s">
         <v>133</v>
       </c>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="51" t="s">
+      <c r="P2" s="49"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="58" t="s">
         <v>134</v>
       </c>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="47"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="50"/>
       <c r="V2" s="12" t="s">
         <v>135</v>
       </c>

--- a/[Document]/소개운영자료/DIVE_개인정보_진로현황_수요조사.xlsx
+++ b/[Document]/소개운영자료/DIVE_개인정보_진로현황_수요조사.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DataScience\[DIVE]\[Document]\소개운영자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD199B00-DB8E-4E81-A54E-E5939B8D84EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69A8FC5-0C98-42CA-9BFC-C16016A36EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31890" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026Y2Q" sheetId="1" r:id="rId1"/>
@@ -57,6 +57,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기수</t>
     </r>
@@ -68,6 +69,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>활동기간</t>
     </r>
@@ -79,6 +81,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>이름</t>
     </r>
@@ -90,6 +93,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>학번</t>
     </r>
@@ -101,6 +105,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>연락처</t>
     </r>
@@ -112,6 +117,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>이메일</t>
     </r>
@@ -137,6 +143,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -157,6 +164,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)
 : 26</t>
@@ -180,6 +188,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>진로현황</t>
     </r>
@@ -191,6 +200,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>실적</t>
     </r>
@@ -200,6 +210,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -209,6 +220,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>최신순</t>
     </r>
@@ -218,6 +230,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -244,6 +257,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>1</t>
     </r>
@@ -264,6 +278,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
@@ -284,6 +299,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>/</t>
     </r>
@@ -304,6 +320,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -326,6 +343,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -346,6 +364,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">: KCI/SCI/SSCI </t>
     </r>
@@ -366,6 +385,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 (</t>
@@ -389,6 +409,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>3</t>
     </r>
@@ -409,6 +430,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
@@ -429,6 +451,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -449,6 +472,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 (</t>
@@ -492,6 +516,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -502,6 +527,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Start Up &gt; </t>
     </r>
@@ -510,6 +536,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>인천대학교</t>
     </r>
@@ -518,6 +545,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -526,6 +554,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -534,6 +563,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> &gt; </t>
     </r>
@@ -542,6 +572,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>삼성리서치 &gt; 삼성전자 &gt; 한국인터넷진흥원 &gt; 대신증권 &gt; 금융감독원 &gt; ...</t>
     </r>
@@ -553,6 +584,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">육아 </t>
     </r>
@@ -562,6 +594,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Daddy 4</t>
     </r>
@@ -571,6 +604,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>년차(딸, 아들 모두 보육 가능)
 육아 인내심 많이 + 책 조금 + 논문 조금 + 영화시청 많이 + 투자 많이 + …</t>
@@ -592,6 +626,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -601,6 +636,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -614,6 +650,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>유효정</t>
     </r>
@@ -633,6 +670,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -641,6 +679,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -649,6 +688,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>컴퓨터공학부</t>
     </r>
@@ -657,6 +697,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -667,6 +708,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>인천대학교</t>
     </r>
@@ -675,14 +717,16 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -691,6 +735,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -699,6 +744,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>컴퓨터공학부</t>
     </r>
@@ -707,6 +753,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -718,6 +765,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2026.02] </t>
     </r>
@@ -727,6 +775,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>한국경영과학회지</t>
     </r>
@@ -736,6 +785,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> | </t>
     </r>
@@ -744,6 +794,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>비형식</t>
     </r>
@@ -752,6 +803,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -760,6 +812,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>평생학습</t>
     </r>
@@ -768,6 +821,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -776,6 +830,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>참여</t>
     </r>
@@ -784,6 +839,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -792,6 +848,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>예측을</t>
     </r>
@@ -800,6 +857,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -808,6 +866,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>위한</t>
     </r>
@@ -816,6 +875,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -824,6 +884,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>설명가능한</t>
     </r>
@@ -832,6 +893,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> AI </t>
     </r>
@@ -840,6 +902,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>의사결정</t>
     </r>
@@ -848,6 +911,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
@@ -856,6 +920,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>디지털</t>
     </r>
@@ -864,6 +929,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>·</t>
     </r>
@@ -872,6 +938,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>고령사회에서의</t>
     </r>
@@ -880,6 +947,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -888,6 +956,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>참여자</t>
     </r>
@@ -896,6 +965,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -904,6 +974,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>예측과</t>
     </r>
@@ -912,6 +983,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -920,6 +992,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>포용적</t>
     </r>
@@ -928,6 +1001,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -936,6 +1010,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>교육정책</t>
     </r>
@@ -945,6 +1020,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 [2025.06] </t>
@@ -955,6 +1031,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>한국빅데이터학회</t>
     </r>
@@ -964,6 +1041,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -973,6 +1051,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>학회지</t>
     </r>
@@ -982,6 +1061,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> | </t>
     </r>
@@ -990,6 +1070,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>설명가능한</t>
     </r>
@@ -998,6 +1079,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1006,6 +1088,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>인공지능</t>
     </r>
@@ -1014,6 +1097,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1022,6 +1106,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>기반</t>
     </r>
@@ -1030,6 +1115,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1038,6 +1124,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>비형식학습</t>
     </r>
@@ -1046,6 +1133,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1054,6 +1142,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>효과성</t>
     </r>
@@ -1062,6 +1151,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1070,6 +1160,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>분석</t>
     </r>
@@ -1078,6 +1169,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1086,6 +1178,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>및</t>
     </r>
@@ -1094,6 +1187,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1102,6 +1196,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>참여자</t>
     </r>
@@ -1110,6 +1205,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1118,6 +1214,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>추천</t>
     </r>
@@ -1126,6 +1223,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1134,6 +1232,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>애널리틱스</t>
     </r>
@@ -1142,6 +1241,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
@@ -1150,6 +1250,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>지속</t>
     </r>
@@ -1158,6 +1259,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1166,6 +1268,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>가능한</t>
     </r>
@@ -1174,6 +1277,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1182,6 +1286,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>평생학습</t>
     </r>
@@ -1190,6 +1295,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1198,6 +1304,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>유도를</t>
     </r>
@@ -1206,6 +1313,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1214,6 +1322,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>위하여</t>
     </r>
@@ -1223,6 +1332,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -1233,6 +1343,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2025.11] </t>
     </r>
@@ -1242,6 +1353,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">한국경영과학회 추계학술대회 경쟁부문 최우수논문상(1위) </t>
     </r>
@@ -1251,6 +1363,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>|</t>
     </r>
@@ -1259,6 +1372,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1267,6 +1381,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">설명가능한 </t>
     </r>
@@ -1275,6 +1390,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">AI </t>
     </r>
@@ -1283,6 +1399,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>기반 평생학습 참여촉진 프로그램 정책: 디지털 전환과 고령사회에서의 시사점</t>
     </r>
@@ -1291,6 +1408,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -1301,6 +1419,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2025.08] </t>
     </r>
@@ -1310,6 +1429,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>인문사회융합인재사업단 AI경진대회 장려상(3위) |</t>
     </r>
@@ -1318,6 +1438,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 뿌리 기업 맞춤형 정책 지원 챗봇</t>
     </r>
@@ -1329,6 +1450,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -1338,6 +1460,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -1348,6 +1471,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>조은지</t>
     </r>
@@ -1367,6 +1491,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>경영학부</t>
     </r>
@@ -1377,6 +1502,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>인천대학교</t>
     </r>
@@ -1385,14 +1511,16 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>경영학부</t>
     </r>
@@ -1404,6 +1532,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2026.02] </t>
     </r>
@@ -1424,6 +1553,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> | </t>
     </r>
@@ -1442,6 +1572,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1460,6 +1591,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1478,6 +1610,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1496,6 +1629,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1514,6 +1648,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1532,6 +1667,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> AI </t>
     </r>
@@ -1550,6 +1686,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
@@ -1568,6 +1705,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>·</t>
     </r>
@@ -1586,6 +1724,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1604,6 +1743,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1622,6 +1762,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1640,6 +1781,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1659,6 +1801,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 [2025.06] </t>
@@ -1680,6 +1823,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1700,6 +1844,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> | </t>
     </r>
@@ -1718,6 +1863,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1736,6 +1882,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1754,6 +1901,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1772,6 +1920,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1790,6 +1939,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1808,6 +1958,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1826,6 +1977,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1844,6 +1996,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1862,6 +2015,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1880,6 +2034,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
@@ -1898,6 +2053,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1916,6 +2072,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1934,6 +2091,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1952,6 +2110,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1971,6 +2130,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -1981,6 +2141,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2025.11] </t>
     </r>
@@ -2001,6 +2162,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>|</t>
     </r>
@@ -2009,6 +2171,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2027,6 +2190,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">AI </t>
     </r>
@@ -2048,6 +2212,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -2057,6 +2222,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -2070,6 +2236,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>방가연</t>
     </r>
@@ -2089,6 +2256,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>미디어커뮤니케이션학과</t>
     </r>
@@ -2097,6 +2265,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -2105,6 +2274,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>산업경영공학부</t>
     </r>
@@ -2113,6 +2283,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -2133,6 +2304,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2151,6 +2323,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -2169,6 +2342,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -2180,6 +2354,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -2189,6 +2364,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -2199,6 +2375,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>강보현</t>
     </r>
@@ -2215,6 +2392,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -2225,6 +2403,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">GTEP </t>
     </r>
@@ -2243,6 +2422,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2264,6 +2444,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -2273,6 +2454,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -2283,6 +2465,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>이현서</t>
     </r>
@@ -2302,6 +2485,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -2310,6 +2494,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -2318,6 +2503,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>컴퓨터공학부</t>
     </r>
@@ -2326,6 +2512,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -2336,6 +2523,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>인천대학교</t>
     </r>
@@ -2344,14 +2532,16 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -2360,6 +2550,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -2368,6 +2559,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>컴퓨터공학부</t>
     </r>
@@ -2376,6 +2568,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -2387,6 +2580,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2026.02] </t>
     </r>
@@ -2396,6 +2590,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>한국경영과학회지</t>
     </r>
@@ -2405,6 +2600,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> | </t>
     </r>
@@ -2413,6 +2609,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>비형식</t>
     </r>
@@ -2421,6 +2618,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2429,6 +2627,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>평생학습</t>
     </r>
@@ -2437,6 +2636,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2445,6 +2645,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>참여</t>
     </r>
@@ -2453,6 +2654,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2461,6 +2663,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>예측을</t>
     </r>
@@ -2469,6 +2672,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2477,6 +2681,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>위한</t>
     </r>
@@ -2485,6 +2690,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2493,6 +2699,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>설명가능한</t>
     </r>
@@ -2501,6 +2708,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> AI </t>
     </r>
@@ -2509,6 +2717,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>의사결정</t>
     </r>
@@ -2517,6 +2726,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
@@ -2525,6 +2735,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>디지털</t>
     </r>
@@ -2533,6 +2744,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>·</t>
     </r>
@@ -2541,6 +2753,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>고령사회에서의</t>
     </r>
@@ -2549,6 +2762,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2557,6 +2771,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>참여자</t>
     </r>
@@ -2565,6 +2780,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2573,6 +2789,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>예측과</t>
     </r>
@@ -2581,6 +2798,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2589,6 +2807,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>포용적</t>
     </r>
@@ -2597,6 +2816,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2605,6 +2825,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>교육정책</t>
     </r>
@@ -2614,6 +2835,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 [2025.06] </t>
@@ -2624,6 +2846,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>한국빅데이터학회</t>
     </r>
@@ -2633,6 +2856,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2642,6 +2866,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>학회지</t>
     </r>
@@ -2651,6 +2876,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> | </t>
     </r>
@@ -2659,6 +2885,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>설명가능한</t>
     </r>
@@ -2667,6 +2894,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2675,6 +2903,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>인공지능</t>
     </r>
@@ -2683,6 +2912,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2691,6 +2921,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>기반</t>
     </r>
@@ -2699,6 +2930,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2707,6 +2939,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>비형식학습</t>
     </r>
@@ -2715,6 +2948,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2723,6 +2957,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>효과성</t>
     </r>
@@ -2731,6 +2966,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2739,6 +2975,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>분석</t>
     </r>
@@ -2747,6 +2984,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2755,6 +2993,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>및</t>
     </r>
@@ -2763,6 +3002,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2771,6 +3011,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>참여자</t>
     </r>
@@ -2779,6 +3020,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2787,6 +3029,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>추천</t>
     </r>
@@ -2795,6 +3038,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2803,6 +3047,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>애널리틱스</t>
     </r>
@@ -2811,6 +3056,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
@@ -2819,6 +3065,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>지속</t>
     </r>
@@ -2827,6 +3074,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2835,6 +3083,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>가능한</t>
     </r>
@@ -2843,6 +3092,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2851,6 +3101,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>평생학습</t>
     </r>
@@ -2859,6 +3110,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2867,6 +3119,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>유도를</t>
     </r>
@@ -2875,6 +3128,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2883,6 +3137,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>위하여</t>
     </r>
@@ -2892,6 +3147,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 [2025.11] </t>
@@ -2902,6 +3158,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">한국경영과학회 추계학술대회 경쟁부문 최우수논문상(1위) </t>
     </r>
@@ -2911,6 +3168,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>|</t>
     </r>
@@ -2919,6 +3177,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2927,6 +3186,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">설명가능한 </t>
     </r>
@@ -2935,6 +3195,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">AI </t>
     </r>
@@ -2943,6 +3204,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>기반 평생학습 참여촉진 프로그램 정책: 디지털 전환과 고령사회에서의 시사점</t>
     </r>
@@ -2951,6 +3213,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -2961,6 +3224,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2025.08] </t>
     </r>
@@ -2970,6 +3234,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>인문사회융합인재사업단 AI경진대회 장려상(3위) |</t>
     </r>
@@ -2978,6 +3243,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 뿌리 기업 맞춤형 정책 지원 챗봇</t>
     </r>
@@ -2989,6 +3255,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -2998,6 +3265,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -3007,6 +3275,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -3016,6 +3285,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>학부연구생</t>
     </r>
@@ -3025,6 +3295,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -3035,6 +3306,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>조성훈</t>
     </r>
@@ -3054,6 +3326,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>인천대학교</t>
     </r>
@@ -3062,14 +3335,16 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>산업경영공학과</t>
     </r>
@@ -3081,6 +3356,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2025.08] </t>
     </r>
@@ -3101,6 +3377,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3121,6 +3398,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3141,6 +3419,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3161,6 +3440,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3181,6 +3461,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>|</t>
     </r>
@@ -3189,6 +3470,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> AI </t>
     </r>
@@ -3207,6 +3489,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3228,6 +3511,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -3237,6 +3521,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -3246,6 +3531,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -3255,6 +3541,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>학부연구생</t>
     </r>
@@ -3264,6 +3551,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -3274,6 +3562,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>이준형</t>
     </r>
@@ -3294,6 +3583,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2025.07] </t>
     </r>
@@ -3314,6 +3604,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3334,6 +3625,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3354,6 +3646,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3374,6 +3667,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3394,6 +3688,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>|</t>
     </r>
@@ -3402,6 +3697,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3420,6 +3716,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> e</t>
     </r>
@@ -3438,6 +3735,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3456,6 +3754,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3474,6 +3773,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3492,6 +3792,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3510,6 +3811,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3528,6 +3830,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3546,6 +3849,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3567,6 +3871,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>3</t>
     </r>
@@ -3576,6 +3881,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -3598,6 +3904,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>수학과</t>
     </r>
@@ -3606,6 +3913,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -3614,6 +3922,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>빅데이터</t>
     </r>
@@ -3622,6 +3931,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3630,6 +3940,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기반</t>
     </r>
@@ -3638,6 +3949,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3646,6 +3958,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>수학적</t>
     </r>
@@ -3654,6 +3967,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3662,6 +3976,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>경영</t>
     </r>
@@ -3670,6 +3985,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -3684,6 +4000,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>3</t>
     </r>
@@ -3693,6 +4010,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -3722,6 +4040,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>3</t>
     </r>
@@ -3731,6 +4050,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -3757,6 +4077,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>3</t>
     </r>
@@ -3766,6 +4087,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -3792,6 +4114,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>3</t>
     </r>
@@ -3801,6 +4124,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -3821,6 +4145,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>3</t>
     </r>
@@ -3830,6 +4155,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -3856,6 +4182,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>3</t>
     </r>
@@ -3865,6 +4192,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -3904,6 +4232,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>26</t>
     </r>
@@ -3926,6 +4255,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기수</t>
     </r>
@@ -3937,6 +4267,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>활동기간</t>
     </r>
@@ -3948,6 +4279,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>이름</t>
     </r>
@@ -3959,6 +4291,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>학번</t>
     </r>
@@ -3970,6 +4303,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>연락처</t>
     </r>
@@ -3981,6 +4315,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>이메일</t>
     </r>
@@ -4003,6 +4338,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -4023,6 +4359,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)
 : 26</t>
@@ -4046,6 +4383,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>진로현황</t>
     </r>
@@ -4057,6 +4395,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>실적</t>
     </r>
@@ -4066,6 +4405,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -4075,6 +4415,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>최신순</t>
     </r>
@@ -4084,6 +4425,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -4104,6 +4446,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기부자</t>
     </r>
@@ -4113,6 +4456,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -4122,6 +4466,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>마케팅</t>
     </r>
@@ -4131,6 +4476,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -4140,6 +4486,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>전략</t>
     </r>
@@ -4149,6 +4496,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(Classification)</t>
     </r>
@@ -4160,6 +4508,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">KTX </t>
     </r>
@@ -4180,6 +4529,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 (Regression)</t>
@@ -4192,6 +4542,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>1</t>
     </r>
@@ -4212,6 +4563,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
@@ -4232,6 +4584,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>/</t>
     </r>
@@ -4252,6 +4605,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -4274,6 +4628,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -4294,6 +4649,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">: KCI/SCI/SSCI </t>
     </r>
@@ -4314,6 +4670,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 (</t>
@@ -4337,6 +4694,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>3</t>
     </r>
@@ -4357,6 +4715,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
@@ -4377,6 +4736,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -4397,6 +4757,7 @@
         <sz val="11"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 (</t>
@@ -4419,6 +4780,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -4429,6 +4791,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Start Up &gt; </t>
     </r>
@@ -4437,6 +4800,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>인천대학교</t>
     </r>
@@ -4445,6 +4809,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -4453,6 +4818,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -4461,6 +4827,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> &gt; </t>
     </r>
@@ -4469,6 +4836,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>삼성리서치 &gt; 삼성전자 &gt; 한국인터넷진흥원 &gt; 대신증권 &gt; 금융감독원 &gt; ...</t>
     </r>
@@ -4480,6 +4848,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">육아 </t>
     </r>
@@ -4489,6 +4858,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Daddy 4</t>
     </r>
@@ -4498,6 +4868,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>년차(딸, 아들 모두 보육 가능)
 육아 인내심 많이 + 책 조금 + 논문 조금 + 영화시청 많이 + 투자 많이 + …</t>
@@ -4510,6 +4881,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>O
 (20</t>
@@ -4520,6 +4892,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>년정도함)</t>
     </r>
@@ -4531,6 +4904,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>O
 (20</t>
@@ -4554,6 +4928,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>O
 (10</t>
@@ -4580,6 +4955,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>1</t>
     </r>
@@ -4589,6 +4965,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -4602,6 +4979,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>손도언</t>
     </r>
@@ -4621,6 +4999,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -4641,6 +5020,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -4659,6 +5039,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> &gt; </t>
     </r>
@@ -4677,6 +5058,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -4698,6 +5080,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>1</t>
     </r>
@@ -4707,6 +5090,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -4717,6 +5101,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>임보민</t>
     </r>
@@ -4736,6 +5121,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -4746,6 +5132,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>동국대학교</t>
     </r>
@@ -4754,14 +5141,16 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>경제학과</t>
     </r>
@@ -4770,6 +5159,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> &gt; </t>
     </r>
@@ -4778,6 +5168,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>인천대학교</t>
     </r>
@@ -4786,14 +5177,16 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -4805,6 +5198,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>[</t>
     </r>
@@ -4825,6 +5219,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">] </t>
     </r>
@@ -4834,6 +5229,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">KCI </t>
     </r>
@@ -4854,6 +5250,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>|</t>
     </r>
@@ -4862,6 +5259,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -4880,6 +5278,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -4898,6 +5297,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -4916,6 +5316,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -4934,6 +5335,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -4952,6 +5354,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -4970,6 +5373,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -4988,6 +5392,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5006,6 +5411,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5024,6 +5430,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5042,6 +5449,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5060,6 +5468,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5078,6 +5487,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5096,6 +5506,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5115,6 +5526,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 [2024.06] SK T&amp;C </t>
@@ -5136,6 +5548,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5155,6 +5568,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Ageism </t>
     </r>
@@ -5173,6 +5587,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5191,6 +5606,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5209,6 +5625,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5227,6 +5644,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5245,6 +5663,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5263,6 +5682,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5281,6 +5701,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5299,6 +5720,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5317,6 +5739,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5335,6 +5758,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5353,6 +5777,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5371,6 +5796,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5389,6 +5815,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5410,6 +5837,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>1</t>
     </r>
@@ -5419,6 +5847,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -5432,6 +5861,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>장민재</t>
     </r>
@@ -5448,6 +5878,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -5468,6 +5899,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5486,6 +5918,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> &gt; </t>
     </r>
@@ -5504,6 +5937,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5525,6 +5959,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>1</t>
     </r>
@@ -5534,6 +5969,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -5543,6 +5979,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -5552,6 +5989,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>학부연구생</t>
     </r>
@@ -5561,6 +5999,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -5571,6 +6010,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>차명주</t>
     </r>
@@ -5587,6 +6027,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -5597,6 +6038,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>하림</t>
     </r>
@@ -5605,6 +6047,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> &gt; </t>
     </r>
@@ -5613,6 +6056,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>인천대학교</t>
     </r>
@@ -5621,14 +6065,16 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -5640,6 +6086,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2025.09] </t>
     </r>
@@ -5649,6 +6096,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>공간정보</t>
     </r>
@@ -5658,6 +6106,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5667,6 +6116,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>활용</t>
     </r>
@@ -5676,6 +6126,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>·</t>
     </r>
@@ -5685,6 +6136,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>아이디어</t>
     </r>
@@ -5694,6 +6146,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5703,6 +6156,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>경진대회</t>
     </r>
@@ -5712,6 +6166,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5721,6 +6176,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">최우수상(2위, 진흥원장상+100만원) </t>
     </r>
@@ -5730,6 +6186,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>|</t>
     </r>
@@ -5738,6 +6195,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5746,6 +6204,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>탑승</t>
     </r>
@@ -5754,6 +6213,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5762,6 +6222,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>가능성</t>
     </r>
@@ -5770,6 +6231,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5778,6 +6240,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>기반</t>
     </r>
@@ -5786,6 +6249,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5794,6 +6258,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>광역버스</t>
     </r>
@@ -5802,6 +6267,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5810,6 +6276,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>정류장</t>
     </r>
@@ -5818,6 +6285,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5826,6 +6294,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>추천</t>
     </r>
@@ -5834,6 +6303,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5842,6 +6312,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>서비스</t>
     </r>
@@ -5850,6 +6321,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> "</t>
     </r>
@@ -5858,6 +6330,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>안기다</t>
     </r>
@@ -5866,6 +6339,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5874,6 +6348,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>버스</t>
     </r>
@@ -5882,6 +6357,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>"(</t>
     </r>
@@ -5890,6 +6366,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>안기다리고</t>
     </r>
@@ -5898,6 +6375,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5906,6 +6384,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>타는</t>
     </r>
@@ -5914,6 +6393,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5922,6 +6402,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>버스</t>
     </r>
@@ -5930,6 +6411,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">)
 </t>
@@ -5940,6 +6422,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2025.06] </t>
     </r>
@@ -5949,6 +6432,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">한국경영과학회 춘계공동학술대회 </t>
     </r>
@@ -5958,6 +6442,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>|</t>
     </r>
@@ -5966,6 +6451,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5974,6 +6460,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>고성능</t>
     </r>
@@ -5982,6 +6469,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5990,6 +6478,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>시계열</t>
     </r>
@@ -5998,6 +6487,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6006,6 +6496,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>딥러닝</t>
     </r>
@@ -6014,6 +6505,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6022,6 +6514,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>알고리즘을</t>
     </r>
@@ -6030,6 +6523,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6038,6 +6532,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>활용한</t>
     </r>
@@ -6046,6 +6541,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6054,6 +6550,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>미래</t>
     </r>
@@ -6062,6 +6559,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6070,6 +6568,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>교통수요</t>
     </r>
@@ -6078,6 +6577,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6086,6 +6586,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">예측
 </t>
@@ -6096,6 +6597,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2025.06] </t>
     </r>
@@ -6105,6 +6607,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>한국빅데이터학회 학회지 |</t>
     </r>
@@ -6113,6 +6616,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 2025년도 KTX 수요 예측 및 정책적 의사결정: XAI 기반 실증적 예측연구
 </t>
@@ -6123,6 +6627,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2024.06] SK T&amp;C </t>
     </r>
@@ -6132,6 +6637,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>재단 보고서 |</t>
     </r>
@@ -6140,6 +6646,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Ageism </t>
     </r>
@@ -6148,6 +6655,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>문제의식</t>
     </r>
@@ -6156,6 +6664,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6164,6 +6673,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>공감대</t>
     </r>
@@ -6172,6 +6682,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6180,6 +6691,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>확산을</t>
     </r>
@@ -6188,6 +6700,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6196,6 +6709,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>위한</t>
     </r>
@@ -6204,6 +6718,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6212,6 +6727,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>한국</t>
     </r>
@@ -6220,6 +6736,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6228,6 +6745,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>사회의</t>
     </r>
@@ -6236,6 +6754,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6244,6 +6763,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>세대간</t>
     </r>
@@ -6252,6 +6772,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6260,6 +6781,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>갈등</t>
     </r>
@@ -6268,6 +6790,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6276,6 +6799,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>트렌드</t>
     </r>
@@ -6284,6 +6808,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6292,6 +6817,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>빅데이터</t>
     </r>
@@ -6300,6 +6826,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6308,6 +6835,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>분석</t>
     </r>
@@ -6316,6 +6844,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6324,6 +6853,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>및</t>
     </r>
@@ -6332,6 +6862,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6340,6 +6871,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>텍스트마이닝</t>
     </r>
@@ -6348,6 +6880,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6356,6 +6889,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>분석</t>
     </r>
@@ -6367,6 +6901,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -6376,6 +6911,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -6386,6 +6922,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>박재흥</t>
     </r>
@@ -6405,6 +6942,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -6413,6 +6951,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -6421,6 +6960,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>컴퓨터공학부</t>
     </r>
@@ -6429,6 +6969,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -6449,6 +6990,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6467,6 +7009,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> &gt; </t>
     </r>
@@ -6485,6 +7028,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6503,6 +7047,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -6521,6 +7066,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -6532,6 +7078,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>[</t>
     </r>
@@ -6552,6 +7099,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">] </t>
     </r>
@@ -6583,6 +7131,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>|</t>
     </r>
@@ -6591,6 +7140,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6609,6 +7159,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6627,6 +7178,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6645,6 +7197,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6663,6 +7216,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6681,6 +7235,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6699,6 +7254,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6717,6 +7273,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6735,6 +7292,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6753,6 +7311,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 
 </t>
@@ -6763,6 +7322,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2025.09] </t>
     </r>
@@ -6783,6 +7343,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>|</t>
     </r>
@@ -6791,6 +7352,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6809,6 +7371,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -6819,6 +7382,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2025.06] </t>
     </r>
@@ -6839,6 +7403,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6859,6 +7424,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>|</t>
     </r>
@@ -6867,6 +7433,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6885,6 +7452,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6903,6 +7471,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6921,6 +7490,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6939,6 +7509,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6957,6 +7528,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6975,6 +7547,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6993,6 +7566,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -7011,6 +7585,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7029,6 +7604,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7047,6 +7623,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7065,6 +7642,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7083,6 +7661,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7104,6 +7683,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -7113,6 +7693,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -7123,6 +7704,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>유효정</t>
     </r>
@@ -7133,6 +7715,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -7141,6 +7724,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -7149,6 +7733,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>컴퓨터공학부</t>
     </r>
@@ -7157,6 +7742,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -7167,6 +7753,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>인천대학교</t>
     </r>
@@ -7175,14 +7762,16 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -7191,6 +7780,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -7199,6 +7789,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>컴퓨터공학부</t>
     </r>
@@ -7207,6 +7798,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -7218,6 +7810,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2026.02] </t>
     </r>
@@ -7227,6 +7820,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>한국경영과학회지</t>
     </r>
@@ -7236,6 +7830,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> | </t>
     </r>
@@ -7244,6 +7839,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>비형식</t>
     </r>
@@ -7252,6 +7848,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7260,6 +7857,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>평생학습</t>
     </r>
@@ -7268,6 +7866,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7276,6 +7875,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>참여</t>
     </r>
@@ -7284,6 +7884,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7292,6 +7893,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>예측을</t>
     </r>
@@ -7300,6 +7902,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7308,6 +7911,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>위한</t>
     </r>
@@ -7316,6 +7920,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7324,6 +7929,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>설명가능한</t>
     </r>
@@ -7332,6 +7938,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> AI </t>
     </r>
@@ -7340,6 +7947,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>의사결정</t>
     </r>
@@ -7348,6 +7956,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
@@ -7356,6 +7965,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>디지털</t>
     </r>
@@ -7364,6 +7974,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>·</t>
     </r>
@@ -7372,6 +7983,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>고령사회에서의</t>
     </r>
@@ -7380,6 +7992,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7388,6 +8001,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>참여자</t>
     </r>
@@ -7396,6 +8010,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7404,6 +8019,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>예측과</t>
     </r>
@@ -7412,6 +8028,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7420,6 +8037,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>포용적</t>
     </r>
@@ -7428,6 +8046,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7436,6 +8055,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>교육정책</t>
     </r>
@@ -7445,6 +8065,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 [2025.06] </t>
@@ -7455,6 +8076,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>한국빅데이터학회</t>
     </r>
@@ -7464,6 +8086,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7473,6 +8096,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>학회지</t>
     </r>
@@ -7482,6 +8106,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> | </t>
     </r>
@@ -7490,6 +8115,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>설명가능한</t>
     </r>
@@ -7498,6 +8124,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7506,6 +8133,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>인공지능</t>
     </r>
@@ -7514,6 +8142,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7522,6 +8151,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>기반</t>
     </r>
@@ -7530,6 +8160,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7538,6 +8169,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>비형식학습</t>
     </r>
@@ -7546,6 +8178,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7554,6 +8187,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>효과성</t>
     </r>
@@ -7562,6 +8196,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7570,6 +8205,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>분석</t>
     </r>
@@ -7578,6 +8214,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7586,6 +8223,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>및</t>
     </r>
@@ -7594,6 +8232,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7602,6 +8241,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>참여자</t>
     </r>
@@ -7610,6 +8250,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7618,6 +8259,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>추천</t>
     </r>
@@ -7626,6 +8268,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7634,6 +8277,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>애널리틱스</t>
     </r>
@@ -7642,6 +8286,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
@@ -7650,6 +8295,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>지속</t>
     </r>
@@ -7658,6 +8304,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7666,6 +8313,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>가능한</t>
     </r>
@@ -7674,6 +8322,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7682,6 +8331,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>평생학습</t>
     </r>
@@ -7690,6 +8340,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7698,6 +8349,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>유도를</t>
     </r>
@@ -7706,6 +8358,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7714,6 +8367,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>위하여</t>
     </r>
@@ -7723,6 +8377,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -7733,6 +8388,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2025.11] </t>
     </r>
@@ -7742,6 +8398,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">한국경영과학회 추계학술대회 경쟁부문 최우수논문상(1위) </t>
     </r>
@@ -7751,6 +8408,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>|</t>
     </r>
@@ -7759,6 +8417,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7767,6 +8426,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">설명가능한 </t>
     </r>
@@ -7775,6 +8435,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">AI </t>
     </r>
@@ -7783,6 +8444,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>기반 평생학습 참여촉진 프로그램 정책: 디지털 전환과 고령사회에서의 시사점</t>
     </r>
@@ -7791,6 +8453,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -7801,6 +8464,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2025.08] </t>
     </r>
@@ -7810,6 +8474,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>인문사회융합인재사업단 AI경진대회 장려상(3위) |</t>
     </r>
@@ -7818,6 +8483,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 뿌리 기업 맞춤형 정책 지원 챗봇</t>
     </r>
@@ -7832,6 +8498,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -7841,6 +8508,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -7851,6 +8519,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>조은지</t>
     </r>
@@ -7861,6 +8530,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>경영학부</t>
     </r>
@@ -7871,6 +8541,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>인천대학교</t>
     </r>
@@ -7879,14 +8550,16 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>경영학부</t>
     </r>
@@ -7898,6 +8571,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2026.02] </t>
     </r>
@@ -7918,6 +8592,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> | </t>
     </r>
@@ -7936,6 +8611,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7954,6 +8630,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7972,6 +8649,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7990,6 +8668,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8008,6 +8687,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8026,6 +8706,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> AI </t>
     </r>
@@ -8044,6 +8725,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
@@ -8062,6 +8744,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>·</t>
     </r>
@@ -8080,6 +8763,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8098,6 +8782,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8116,6 +8801,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8134,6 +8820,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8153,6 +8840,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 [2025.06] </t>
@@ -8174,6 +8862,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8194,6 +8883,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> | </t>
     </r>
@@ -8212,6 +8902,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8230,6 +8921,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8248,6 +8940,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8266,6 +8959,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8284,6 +8978,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8302,6 +8997,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8320,6 +9016,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8338,6 +9035,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8356,6 +9054,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8374,6 +9073,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
@@ -8392,6 +9092,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8410,6 +9111,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8428,6 +9130,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8446,6 +9149,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8465,6 +9169,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -8475,6 +9180,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2025.11] </t>
     </r>
@@ -8495,6 +9201,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>|</t>
     </r>
@@ -8503,6 +9210,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8521,6 +9229,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">AI </t>
     </r>
@@ -8546,6 +9255,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>X
 (</t>
@@ -8568,6 +9278,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -8577,6 +9288,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -8587,6 +9299,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>방가연</t>
     </r>
@@ -8597,6 +9310,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>미디어커뮤니케이션학과</t>
     </r>
@@ -8605,6 +9319,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -8613,6 +9328,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>산업경영공학부</t>
     </r>
@@ -8621,6 +9337,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -8641,6 +9358,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8659,6 +9377,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -8677,6 +9396,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -8687,6 +9407,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>O
 (</t>
@@ -8709,6 +9430,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -8718,6 +9440,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -8728,6 +9451,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>강보현</t>
     </r>
@@ -8738,6 +9462,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -8748,6 +9473,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">GTEP </t>
     </r>
@@ -8766,6 +9492,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8786,6 +9513,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>O
 (</t>
@@ -8808,6 +9536,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -8817,6 +9546,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -8827,6 +9557,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>이현서</t>
     </r>
@@ -8837,6 +9568,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -8845,6 +9577,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -8853,6 +9586,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>컴퓨터공학부</t>
     </r>
@@ -8861,6 +9595,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -8871,6 +9606,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>인천대학교</t>
     </r>
@@ -8879,14 +9615,16 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>무역학부</t>
     </r>
@@ -8895,6 +9633,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -8903,6 +9642,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>컴퓨터공학부</t>
     </r>
@@ -8911,6 +9651,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -8922,6 +9663,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2026.02] </t>
     </r>
@@ -8931,6 +9673,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>한국경영과학회지</t>
     </r>
@@ -8940,6 +9683,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> | </t>
     </r>
@@ -8948,6 +9692,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>비형식</t>
     </r>
@@ -8956,6 +9701,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8964,6 +9710,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>평생학습</t>
     </r>
@@ -8972,6 +9719,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8980,6 +9728,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>참여</t>
     </r>
@@ -8988,6 +9737,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8996,6 +9746,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>예측을</t>
     </r>
@@ -9004,6 +9755,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9012,6 +9764,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>위한</t>
     </r>
@@ -9020,6 +9773,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9028,6 +9782,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>설명가능한</t>
     </r>
@@ -9036,6 +9791,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> AI </t>
     </r>
@@ -9044,6 +9800,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>의사결정</t>
     </r>
@@ -9052,6 +9809,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
@@ -9060,6 +9818,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>디지털</t>
     </r>
@@ -9068,6 +9827,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>·</t>
     </r>
@@ -9076,6 +9836,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>고령사회에서의</t>
     </r>
@@ -9084,6 +9845,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9092,6 +9854,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>참여자</t>
     </r>
@@ -9100,6 +9863,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9108,6 +9872,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>예측과</t>
     </r>
@@ -9116,6 +9881,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9124,6 +9890,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>포용적</t>
     </r>
@@ -9132,6 +9899,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9140,6 +9908,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>교육정책</t>
     </r>
@@ -9149,6 +9918,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 [2025.06] </t>
@@ -9159,6 +9929,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>한국빅데이터학회</t>
     </r>
@@ -9168,6 +9939,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9177,6 +9949,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>학회지</t>
     </r>
@@ -9186,6 +9959,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> | </t>
     </r>
@@ -9194,6 +9968,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>설명가능한</t>
     </r>
@@ -9202,6 +9977,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9210,6 +9986,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>인공지능</t>
     </r>
@@ -9218,6 +9995,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9226,6 +10004,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>기반</t>
     </r>
@@ -9234,6 +10013,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9242,6 +10022,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>비형식학습</t>
     </r>
@@ -9250,6 +10031,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9258,6 +10040,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>효과성</t>
     </r>
@@ -9266,6 +10049,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9274,6 +10058,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>분석</t>
     </r>
@@ -9282,6 +10067,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9290,6 +10076,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>및</t>
     </r>
@@ -9298,6 +10085,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9306,6 +10094,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>참여자</t>
     </r>
@@ -9314,6 +10103,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9322,6 +10112,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>추천</t>
     </r>
@@ -9330,6 +10121,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9338,6 +10130,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>애널리틱스</t>
     </r>
@@ -9346,6 +10139,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
@@ -9354,6 +10148,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>지속</t>
     </r>
@@ -9362,6 +10157,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9370,6 +10166,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>가능한</t>
     </r>
@@ -9378,6 +10175,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9386,6 +10184,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>평생학습</t>
     </r>
@@ -9394,6 +10193,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9402,6 +10202,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>유도를</t>
     </r>
@@ -9410,6 +10211,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9418,6 +10220,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>위하여</t>
     </r>
@@ -9427,6 +10230,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 [2025.11] </t>
@@ -9437,6 +10241,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">한국경영과학회 추계학술대회 경쟁부문 최우수논문상(1위) </t>
     </r>
@@ -9446,6 +10251,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>|</t>
     </r>
@@ -9454,6 +10260,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9462,6 +10269,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">설명가능한 </t>
     </r>
@@ -9470,6 +10278,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">AI </t>
     </r>
@@ -9478,6 +10287,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>기반 평생학습 참여촉진 프로그램 정책: 디지털 전환과 고령사회에서의 시사점</t>
     </r>
@@ -9486,6 +10296,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -9496,6 +10307,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2025.08] </t>
     </r>
@@ -9505,6 +10317,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>인문사회융합인재사업단 AI경진대회 장려상(3위) |</t>
     </r>
@@ -9513,6 +10326,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 뿌리 기업 맞춤형 정책 지원 챗봇</t>
     </r>
@@ -9523,6 +10337,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>O
 (대학원준비</t>
@@ -9532,6 +10347,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -9543,6 +10359,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -9552,6 +10369,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -9561,6 +10379,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -9570,6 +10389,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>학부연구생</t>
     </r>
@@ -9579,6 +10399,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -9589,6 +10410,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>조성훈</t>
     </r>
@@ -9599,6 +10421,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>인천대학교</t>
     </r>
@@ -9607,14 +10430,16 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>산업경영공학과</t>
     </r>
@@ -9626,6 +10451,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2025.08] </t>
     </r>
@@ -9646,6 +10472,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9666,6 +10493,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9686,6 +10514,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9706,6 +10535,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9726,6 +10556,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>|</t>
     </r>
@@ -9734,6 +10565,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> AI </t>
     </r>
@@ -9752,6 +10584,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9773,6 +10606,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -9782,6 +10616,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -9791,6 +10626,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -9800,6 +10636,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>학부연구생</t>
     </r>
@@ -9809,6 +10646,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -9819,6 +10657,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>이준형</t>
     </r>
@@ -9830,6 +10669,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[2025.07] </t>
     </r>
@@ -9850,6 +10690,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9870,6 +10711,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9890,6 +10732,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9910,6 +10753,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9930,6 +10774,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>|</t>
     </r>
@@ -9938,6 +10783,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9956,6 +10802,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> e</t>
     </r>
@@ -9974,6 +10821,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9992,6 +10840,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -10010,6 +10859,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -10028,6 +10878,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -10046,6 +10897,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -10064,6 +10916,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -10082,6 +10935,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -10107,6 +10961,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>O
 (</t>
@@ -10126,6 +10981,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -10137,6 +10993,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>3</t>
     </r>
@@ -10146,6 +11003,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -10156,6 +11014,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>수학과</t>
     </r>
@@ -10164,6 +11023,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -10172,6 +11032,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>빅데이터</t>
     </r>
@@ -10180,6 +11041,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -10188,6 +11050,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기반</t>
     </r>
@@ -10196,6 +11059,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -10204,6 +11068,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>수학적</t>
     </r>
@@ -10212,6 +11077,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -10220,6 +11086,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>경영</t>
     </r>
@@ -10228,6 +11095,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -10241,6 +11109,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>O
 (</t>
@@ -10250,6 +11119,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>스터디집중)</t>
     </r>
@@ -10261,6 +11131,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>3</t>
     </r>
@@ -10270,6 +11141,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -10281,6 +11153,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>3</t>
     </r>
@@ -10290,6 +11163,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -10300,6 +11174,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>O
 (</t>
@@ -10309,6 +11184,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>공모전집중)</t>
     </r>
@@ -10320,6 +11196,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>3</t>
     </r>
@@ -10329,6 +11206,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -10339,6 +11217,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>X
 (</t>
@@ -10371,6 +11250,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>3</t>
     </r>
@@ -10380,6 +11260,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -10390,6 +11271,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>X
 (</t>
@@ -10412,6 +11294,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>3</t>
     </r>
@@ -10421,6 +11304,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -10435,6 +11319,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>O
 (</t>
@@ -10457,6 +11342,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>3</t>
     </r>
@@ -10466,6 +11352,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>기</t>
     </r>
@@ -10476,6 +11363,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>O
 (26</t>
@@ -10658,7 +11546,8 @@
         <charset val="129"/>
       </rPr>
       <t>논문 1건
-- 데이터: https://drive.google.com/drive/folders/1cX1QUZgE5ZihPZmlJxIcao_KCacXF8vR</t>
+- 데이터: https://drive.google.com/drive/folders/1cX1QUZgE5ZihPZmlJxIcao_
+2. 공모전/학회발표 1건</t>
     </r>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
@@ -10685,29 +11574,34 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -10723,11 +11617,13 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -10742,30 +11638,35 @@
       <sz val="20"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
       <color theme="0"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -10778,24 +11679,28 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -10809,12 +11714,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -10836,6 +11743,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -10856,6 +11764,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -11404,22 +12313,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U220"/>
-  <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.53125" customWidth="1"/>
+    <col min="1" max="1" width="16.5546875" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="11.1328125" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="7" width="11.1328125" customWidth="1"/>
-    <col min="8" max="8" width="17.53125" customWidth="1"/>
-    <col min="9" max="9" width="32.3984375" customWidth="1"/>
-    <col min="10" max="10" width="70.53125" customWidth="1"/>
-    <col min="11" max="11" width="13.53125" customWidth="1"/>
-    <col min="12" max="20" width="14.53125" customWidth="1"/>
+    <col min="6" max="7" width="11.109375" customWidth="1"/>
+    <col min="8" max="8" width="17.5546875" customWidth="1"/>
+    <col min="9" max="9" width="32.44140625" customWidth="1"/>
+    <col min="10" max="10" width="70.5546875" customWidth="1"/>
+    <col min="11" max="11" width="13.5546875" customWidth="1"/>
+    <col min="12" max="20" width="14.5546875" customWidth="1"/>
     <col min="21" max="21" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="18">
+    <row r="1" spans="1:21" ht="18.600000000000001">
       <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
@@ -11468,7 +12377,7 @@
       <c r="T2" s="54"/>
       <c r="U2" s="54"/>
     </row>
-    <row r="3" spans="1:21" ht="84.4">
+    <row r="3" spans="1:21" ht="104.4">
       <c r="A3" s="9" t="s">
         <v>6</v>
       </c>
@@ -11533,7 +12442,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="41.25">
+    <row r="4" spans="1:21" ht="55.8">
       <c r="A4" s="14" t="s">
         <v>25</v>
       </c>
@@ -11594,7 +12503,7 @@
       </c>
       <c r="U4" s="22"/>
     </row>
-    <row r="5" spans="1:21" ht="127.5">
+    <row r="5" spans="1:21" ht="129">
       <c r="A5" s="24" t="s">
         <v>37</v>
       </c>
@@ -11639,7 +12548,7 @@
       <c r="T5" s="29"/>
       <c r="U5" s="29"/>
     </row>
-    <row r="6" spans="1:21" ht="118.15">
+    <row r="6" spans="1:21" ht="121.8">
       <c r="A6" s="24" t="s">
         <v>46</v>
       </c>
@@ -11690,7 +12599,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="50.65">
+    <row r="7" spans="1:21" ht="52.2">
       <c r="A7" s="24" t="s">
         <v>54</v>
       </c>
@@ -11735,7 +12644,7 @@
       <c r="T7" s="29"/>
       <c r="U7" s="29"/>
     </row>
-    <row r="8" spans="1:21" ht="28.5">
+    <row r="8" spans="1:21" ht="43.2">
       <c r="A8" s="24" t="s">
         <v>62</v>
       </c>
@@ -11774,7 +12683,7 @@
       <c r="T8" s="29"/>
       <c r="U8" s="29"/>
     </row>
-    <row r="9" spans="1:21" ht="127.5">
+    <row r="9" spans="1:21" ht="129">
       <c r="A9" s="24" t="s">
         <v>68</v>
       </c>
@@ -11823,7 +12732,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="28.5">
+    <row r="10" spans="1:21" ht="28.8">
       <c r="A10" s="24" t="s">
         <v>76</v>
       </c>
@@ -11864,7 +12773,7 @@
       <c r="T10" s="26"/>
       <c r="U10" s="26"/>
     </row>
-    <row r="11" spans="1:21" ht="33.75">
+    <row r="11" spans="1:21" ht="34.799999999999997">
       <c r="A11" s="24" t="s">
         <v>83</v>
       </c>
@@ -11913,7 +12822,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="33.75">
+    <row r="12" spans="1:21" ht="34.799999999999997">
       <c r="A12" s="24" t="s">
         <v>89</v>
       </c>
@@ -11958,7 +12867,7 @@
       <c r="T12" s="30"/>
       <c r="U12" s="30"/>
     </row>
-    <row r="13" spans="1:21" ht="28.5">
+    <row r="13" spans="1:21" ht="43.2">
       <c r="A13" s="24" t="s">
         <v>96</v>
       </c>
@@ -12005,7 +12914,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="84.4">
+    <row r="14" spans="1:21" ht="104.4">
       <c r="A14" s="24" t="s">
         <v>103</v>
       </c>
@@ -12048,11 +12957,11 @@
         <v>34</v>
       </c>
       <c r="T14" s="29"/>
-      <c r="U14" s="45" t="s">
+      <c r="U14" s="29" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="33.75">
+    <row r="15" spans="1:21" ht="34.799999999999997">
       <c r="A15" s="24" t="s">
         <v>109</v>
       </c>
@@ -12097,7 +13006,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="28.5">
+    <row r="16" spans="1:21" ht="43.2">
       <c r="A16" s="24" t="s">
         <v>115</v>
       </c>
@@ -12136,7 +13045,7 @@
       <c r="T16" s="29"/>
       <c r="U16" s="29"/>
     </row>
-    <row r="17" spans="1:21" ht="33.75">
+    <row r="17" spans="1:21" ht="52.2">
       <c r="A17" s="24" t="s">
         <v>119</v>
       </c>
@@ -12185,7 +13094,7 @@
       <c r="T17" s="29"/>
       <c r="U17" s="29"/>
     </row>
-    <row r="18" spans="1:21" ht="28.5">
+    <row r="18" spans="1:21" ht="28.8">
       <c r="A18" s="24" t="s">
         <v>125</v>
       </c>
@@ -13873,19 +14782,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:V999"/>
-  <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.53125" customWidth="1"/>
+    <col min="1" max="1" width="16.5546875" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="11.1328125" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="7" width="11.1328125" customWidth="1"/>
-    <col min="8" max="8" width="17.53125" customWidth="1"/>
-    <col min="9" max="9" width="32.3984375" customWidth="1"/>
-    <col min="10" max="10" width="70.53125" customWidth="1"/>
-    <col min="11" max="21" width="14.53125" customWidth="1"/>
-    <col min="22" max="22" width="13.53125" customWidth="1"/>
-    <col min="23" max="25" width="8.86328125" customWidth="1"/>
+    <col min="6" max="7" width="11.109375" customWidth="1"/>
+    <col min="8" max="8" width="17.5546875" customWidth="1"/>
+    <col min="9" max="9" width="32.44140625" customWidth="1"/>
+    <col min="10" max="10" width="70.5546875" customWidth="1"/>
+    <col min="11" max="21" width="14.5546875" customWidth="1"/>
+    <col min="22" max="22" width="13.5546875" customWidth="1"/>
+    <col min="23" max="25" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="14.25" customHeight="1">
